--- a/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>GRP.U</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>331200</v>
+        <v>385200</v>
       </c>
       <c r="E8" s="3">
-        <v>286100</v>
+        <v>336700</v>
       </c>
       <c r="F8" s="3">
-        <v>247300</v>
+        <v>290800</v>
       </c>
       <c r="G8" s="3">
-        <v>199000</v>
+        <v>251400</v>
       </c>
       <c r="H8" s="3">
-        <v>179900</v>
+        <v>202200</v>
       </c>
       <c r="I8" s="3">
-        <v>177900</v>
+        <v>182900</v>
       </c>
       <c r="J8" s="3">
-        <v>162400</v>
+        <v>180800</v>
       </c>
       <c r="K8" s="3">
         <v>162400</v>
       </c>
       <c r="L8" s="3">
+        <v>162400</v>
+      </c>
+      <c r="M8" s="3">
         <v>162800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>146200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>136300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>139000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>54700</v>
+        <v>63600</v>
       </c>
       <c r="E9" s="3">
-        <v>44200</v>
+        <v>55600</v>
       </c>
       <c r="F9" s="3">
-        <v>34300</v>
+        <v>44900</v>
       </c>
       <c r="G9" s="3">
-        <v>25700</v>
+        <v>34900</v>
       </c>
       <c r="H9" s="3">
-        <v>22500</v>
+        <v>26100</v>
       </c>
       <c r="I9" s="3">
-        <v>22800</v>
+        <v>22900</v>
       </c>
       <c r="J9" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K9" s="3">
         <v>5600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32800</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>276500</v>
+        <v>321600</v>
       </c>
       <c r="E10" s="3">
-        <v>241900</v>
+        <v>281100</v>
       </c>
       <c r="F10" s="3">
-        <v>213000</v>
+        <v>245800</v>
       </c>
       <c r="G10" s="3">
-        <v>173300</v>
+        <v>216500</v>
       </c>
       <c r="H10" s="3">
+        <v>176100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>160000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>157700</v>
+      </c>
+      <c r="K10" s="3">
+        <v>156900</v>
+      </c>
+      <c r="L10" s="3">
+        <v>157100</v>
+      </c>
+      <c r="M10" s="3">
         <v>157400</v>
       </c>
-      <c r="I10" s="3">
-        <v>155100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>156900</v>
-      </c>
-      <c r="K10" s="3">
-        <v>157100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>157400</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>137600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>99900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106200</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,74 +960,80 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>15000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
-        <v>800</v>
-      </c>
       <c r="G15" s="3">
+        <v>900</v>
+      </c>
+      <c r="H15" s="3">
         <v>700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1020,17 +1042,20 @@
         <v>500</v>
       </c>
       <c r="M15" s="3">
+        <v>500</v>
+      </c>
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>112300</v>
+        <v>148400</v>
       </c>
       <c r="E17" s="3">
-        <v>101400</v>
+        <v>114100</v>
       </c>
       <c r="F17" s="3">
-        <v>80200</v>
+        <v>103100</v>
       </c>
       <c r="G17" s="3">
-        <v>65200</v>
+        <v>81500</v>
       </c>
       <c r="H17" s="3">
-        <v>57400</v>
+        <v>66300</v>
       </c>
       <c r="I17" s="3">
-        <v>61300</v>
+        <v>58400</v>
       </c>
       <c r="J17" s="3">
+        <v>62400</v>
+      </c>
+      <c r="K17" s="3">
         <v>40400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>97900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>219000</v>
+        <v>236800</v>
       </c>
       <c r="E18" s="3">
-        <v>184600</v>
+        <v>222600</v>
       </c>
       <c r="F18" s="3">
-        <v>167100</v>
+        <v>187700</v>
       </c>
       <c r="G18" s="3">
-        <v>133800</v>
+        <v>169900</v>
       </c>
       <c r="H18" s="3">
-        <v>122500</v>
+        <v>136000</v>
       </c>
       <c r="I18" s="3">
-        <v>116500</v>
+        <v>124500</v>
       </c>
       <c r="J18" s="3">
+        <v>118500</v>
+      </c>
+      <c r="K18" s="3">
         <v>122100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>121500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>118400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>94000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>96800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-152000</v>
+        <v>-141500</v>
       </c>
       <c r="E20" s="3">
-        <v>942900</v>
+        <v>-154500</v>
       </c>
       <c r="F20" s="3">
-        <v>195700</v>
+        <v>958400</v>
       </c>
       <c r="G20" s="3">
-        <v>175100</v>
+        <v>198900</v>
       </c>
       <c r="H20" s="3">
-        <v>254100</v>
+        <v>178000</v>
       </c>
       <c r="I20" s="3">
-        <v>153300</v>
+        <v>258300</v>
       </c>
       <c r="J20" s="3">
+        <v>155800</v>
+      </c>
+      <c r="K20" s="3">
         <v>116600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>52500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-61700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>24800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>68200</v>
+        <v>96300</v>
       </c>
       <c r="E21" s="3">
-        <v>1128400</v>
+        <v>69300</v>
       </c>
       <c r="F21" s="3">
-        <v>363600</v>
+        <v>1147000</v>
       </c>
       <c r="G21" s="3">
-        <v>309600</v>
+        <v>369600</v>
       </c>
       <c r="H21" s="3">
-        <v>376800</v>
+        <v>314700</v>
       </c>
       <c r="I21" s="3">
-        <v>270100</v>
+        <v>383000</v>
       </c>
       <c r="J21" s="3">
+        <v>274500</v>
+      </c>
+      <c r="K21" s="3">
         <v>239200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>174500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>57100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>85300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>121800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>74100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>67000</v>
+        <v>95300</v>
       </c>
       <c r="E23" s="3">
-        <v>1127500</v>
+        <v>68100</v>
       </c>
       <c r="F23" s="3">
-        <v>362800</v>
+        <v>1146100</v>
       </c>
       <c r="G23" s="3">
-        <v>308900</v>
+        <v>368800</v>
       </c>
       <c r="H23" s="3">
-        <v>376600</v>
+        <v>314000</v>
       </c>
       <c r="I23" s="3">
-        <v>269800</v>
+        <v>382800</v>
       </c>
       <c r="J23" s="3">
+        <v>274300</v>
+      </c>
+      <c r="K23" s="3">
         <v>238700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>174000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>56600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>84900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>121600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-46300</v>
+        <v>-7000</v>
       </c>
       <c r="E24" s="3">
-        <v>174900</v>
+        <v>-47000</v>
       </c>
       <c r="F24" s="3">
-        <v>50200</v>
+        <v>177800</v>
       </c>
       <c r="G24" s="3">
-        <v>31000</v>
+        <v>51100</v>
       </c>
       <c r="H24" s="3">
-        <v>38300</v>
+        <v>31500</v>
       </c>
       <c r="I24" s="3">
-        <v>9800</v>
+        <v>38900</v>
       </c>
       <c r="J24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K24" s="3">
         <v>34600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-25500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>113300</v>
+        <v>102300</v>
       </c>
       <c r="E26" s="3">
-        <v>952600</v>
+        <v>115200</v>
       </c>
       <c r="F26" s="3">
-        <v>312600</v>
+        <v>968300</v>
       </c>
       <c r="G26" s="3">
-        <v>277900</v>
+        <v>317700</v>
       </c>
       <c r="H26" s="3">
-        <v>338300</v>
+        <v>282500</v>
       </c>
       <c r="I26" s="3">
-        <v>260100</v>
+        <v>343900</v>
       </c>
       <c r="J26" s="3">
+        <v>264400</v>
+      </c>
+      <c r="K26" s="3">
         <v>204100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>146800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>50000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>110400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>112800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>113200</v>
+        <v>101000</v>
       </c>
       <c r="E27" s="3">
-        <v>952300</v>
+        <v>115100</v>
       </c>
       <c r="F27" s="3">
-        <v>312500</v>
+        <v>968000</v>
       </c>
       <c r="G27" s="3">
-        <v>277800</v>
+        <v>317600</v>
       </c>
       <c r="H27" s="3">
-        <v>338200</v>
+        <v>282400</v>
       </c>
       <c r="I27" s="3">
-        <v>260100</v>
+        <v>343700</v>
       </c>
       <c r="J27" s="3">
+        <v>264300</v>
+      </c>
+      <c r="K27" s="3">
         <v>203100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>49800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>110200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>112700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,24 +1610,27 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>5300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1400</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>72600</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>152000</v>
+        <v>141500</v>
       </c>
       <c r="E32" s="3">
-        <v>-942900</v>
+        <v>154500</v>
       </c>
       <c r="F32" s="3">
-        <v>-195700</v>
+        <v>-958400</v>
       </c>
       <c r="G32" s="3">
-        <v>-175100</v>
+        <v>-198900</v>
       </c>
       <c r="H32" s="3">
-        <v>-254100</v>
+        <v>-178000</v>
       </c>
       <c r="I32" s="3">
-        <v>-153300</v>
+        <v>-258300</v>
       </c>
       <c r="J32" s="3">
+        <v>-155800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-116600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-52500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>61700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-24800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>113200</v>
+        <v>101000</v>
       </c>
       <c r="E33" s="3">
-        <v>952300</v>
+        <v>115100</v>
       </c>
       <c r="F33" s="3">
-        <v>312500</v>
+        <v>968000</v>
       </c>
       <c r="G33" s="3">
-        <v>277800</v>
+        <v>317600</v>
       </c>
       <c r="H33" s="3">
-        <v>338200</v>
+        <v>282400</v>
       </c>
       <c r="I33" s="3">
-        <v>260100</v>
+        <v>343700</v>
       </c>
       <c r="J33" s="3">
+        <v>264300</v>
+      </c>
+      <c r="K33" s="3">
         <v>203100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>145200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>55100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>111600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>112700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117100</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>113200</v>
+        <v>101000</v>
       </c>
       <c r="E35" s="3">
-        <v>952300</v>
+        <v>115100</v>
       </c>
       <c r="F35" s="3">
-        <v>312500</v>
+        <v>968000</v>
       </c>
       <c r="G35" s="3">
-        <v>277800</v>
+        <v>317600</v>
       </c>
       <c r="H35" s="3">
-        <v>338200</v>
+        <v>282400</v>
       </c>
       <c r="I35" s="3">
-        <v>260100</v>
+        <v>343700</v>
       </c>
       <c r="J35" s="3">
+        <v>264300</v>
+      </c>
+      <c r="K35" s="3">
         <v>203100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>145200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>55100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>111600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>112700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117100</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,79 +1986,83 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>92400</v>
+        <v>85500</v>
       </c>
       <c r="E41" s="3">
-        <v>292200</v>
+        <v>93900</v>
       </c>
       <c r="F41" s="3">
-        <v>567800</v>
+        <v>297000</v>
       </c>
       <c r="G41" s="3">
-        <v>180700</v>
+        <v>577100</v>
       </c>
       <c r="H41" s="3">
-        <v>388900</v>
+        <v>183600</v>
       </c>
       <c r="I41" s="3">
-        <v>40400</v>
+        <v>395300</v>
       </c>
       <c r="J41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="K41" s="3">
         <v>79500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>73500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5800</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
-        <v>36600</v>
-      </c>
       <c r="G42" s="3">
-        <v>36500</v>
+        <v>37200</v>
       </c>
       <c r="H42" s="3">
-        <v>89600</v>
+        <v>37100</v>
       </c>
       <c r="I42" s="3">
-        <v>9700</v>
+        <v>91100</v>
       </c>
       <c r="J42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K42" s="3">
         <v>99500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>41100</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
@@ -1984,51 +2073,57 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>60100</v>
+        <v>9400</v>
       </c>
       <c r="E43" s="3">
-        <v>8900</v>
+        <v>61100</v>
       </c>
       <c r="F43" s="3">
-        <v>5600</v>
+        <v>9000</v>
       </c>
       <c r="G43" s="3">
-        <v>14400</v>
+        <v>5700</v>
       </c>
       <c r="H43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,93 +2163,102 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>40600</v>
+        <v>16900</v>
       </c>
       <c r="E45" s="3">
-        <v>52200</v>
+        <v>41300</v>
       </c>
       <c r="F45" s="3">
-        <v>5000</v>
+        <v>53100</v>
       </c>
       <c r="G45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
-        <v>34300</v>
-      </c>
       <c r="I45" s="3">
-        <v>286400</v>
+        <v>34900</v>
       </c>
       <c r="J45" s="3">
+        <v>291200</v>
+      </c>
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>198900</v>
+        <v>112100</v>
       </c>
       <c r="E46" s="3">
-        <v>353700</v>
+        <v>202200</v>
       </c>
       <c r="F46" s="3">
-        <v>614900</v>
+        <v>359500</v>
       </c>
       <c r="G46" s="3">
-        <v>234000</v>
+        <v>625100</v>
       </c>
       <c r="H46" s="3">
-        <v>516200</v>
+        <v>237800</v>
       </c>
       <c r="I46" s="3">
-        <v>338400</v>
+        <v>524700</v>
       </c>
       <c r="J46" s="3">
+        <v>344000</v>
+      </c>
+      <c r="K46" s="3">
         <v>182200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>99000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>80600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2162,13 +2266,13 @@
         <v>200</v>
       </c>
       <c r="E47" s="3">
-        <v>7800</v>
+        <v>200</v>
       </c>
       <c r="F47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G47" s="3">
         <v>300</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -2176,8 +2280,8 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>400</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>400</v>
@@ -2189,56 +2293,62 @@
         <v>400</v>
       </c>
       <c r="N47" s="3">
+        <v>400</v>
+      </c>
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6429400</v>
+        <v>6511500</v>
       </c>
       <c r="E48" s="3">
-        <v>5796900</v>
+        <v>6535300</v>
       </c>
       <c r="F48" s="3">
-        <v>4259500</v>
+        <v>5892400</v>
       </c>
       <c r="G48" s="3">
-        <v>3242500</v>
+        <v>4329600</v>
       </c>
       <c r="H48" s="3">
-        <v>2490600</v>
+        <v>3295900</v>
       </c>
       <c r="I48" s="3">
-        <v>1988000</v>
+        <v>2531600</v>
       </c>
       <c r="J48" s="3">
+        <v>2020800</v>
+      </c>
+      <c r="K48" s="3">
         <v>1929400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1947400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1815100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1812000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2321200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>515800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2278,9 +2388,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>118400</v>
+        <v>76200</v>
       </c>
       <c r="E52" s="3">
-        <v>69600</v>
+        <v>120400</v>
       </c>
       <c r="F52" s="3">
-        <v>30800</v>
+        <v>70800</v>
       </c>
       <c r="G52" s="3">
-        <v>16100</v>
+        <v>31300</v>
       </c>
       <c r="H52" s="3">
-        <v>38500</v>
+        <v>16300</v>
       </c>
       <c r="I52" s="3">
+        <v>39200</v>
+      </c>
+      <c r="J52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6746900</v>
+        <v>6700000</v>
       </c>
       <c r="E54" s="3">
-        <v>6228100</v>
+        <v>6858100</v>
       </c>
       <c r="F54" s="3">
-        <v>4905500</v>
+        <v>6330700</v>
       </c>
       <c r="G54" s="3">
-        <v>3492500</v>
+        <v>4986300</v>
       </c>
       <c r="H54" s="3">
-        <v>3045300</v>
+        <v>3550100</v>
       </c>
       <c r="I54" s="3">
-        <v>2331100</v>
+        <v>3095400</v>
       </c>
       <c r="J54" s="3">
+        <v>2369500</v>
+      </c>
+      <c r="K54" s="3">
         <v>2116800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2051200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1921600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1900400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1510900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>956800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8100</v>
+        <v>8400</v>
       </c>
       <c r="E57" s="3">
-        <v>3900</v>
+        <v>8300</v>
       </c>
       <c r="F57" s="3">
-        <v>7200</v>
+        <v>4000</v>
       </c>
       <c r="G57" s="3">
-        <v>5000</v>
+        <v>7300</v>
       </c>
       <c r="H57" s="3">
-        <v>3900</v>
+        <v>5100</v>
       </c>
       <c r="I57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>328500</v>
+        <v>181000</v>
       </c>
       <c r="E58" s="3">
+        <v>333900</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
-        <v>182300</v>
-      </c>
       <c r="G58" s="3">
+        <v>185300</v>
+      </c>
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>23700</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>24100</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>30200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>40900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>113600</v>
+        <v>94700</v>
       </c>
       <c r="E59" s="3">
-        <v>115200</v>
+        <v>115500</v>
       </c>
       <c r="F59" s="3">
-        <v>82400</v>
+        <v>117100</v>
       </c>
       <c r="G59" s="3">
-        <v>56400</v>
+        <v>83800</v>
       </c>
       <c r="H59" s="3">
+        <v>57400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>58600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>57300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>38400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>43800</v>
+      </c>
+      <c r="M59" s="3">
+        <v>47700</v>
+      </c>
+      <c r="N59" s="3">
+        <v>36800</v>
+      </c>
+      <c r="O59" s="3">
         <v>57600</v>
       </c>
-      <c r="I59" s="3">
-        <v>56400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>38400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>43800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>47700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>36800</v>
-      </c>
-      <c r="N59" s="3">
-        <v>57600</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>450300</v>
+        <v>284100</v>
       </c>
       <c r="E60" s="3">
-        <v>119500</v>
+        <v>457700</v>
       </c>
       <c r="F60" s="3">
-        <v>271800</v>
+        <v>121500</v>
       </c>
       <c r="G60" s="3">
-        <v>61900</v>
+        <v>276300</v>
       </c>
       <c r="H60" s="3">
-        <v>61500</v>
+        <v>62900</v>
       </c>
       <c r="I60" s="3">
-        <v>84100</v>
+        <v>62500</v>
       </c>
       <c r="J60" s="3">
+        <v>85500</v>
+      </c>
+      <c r="K60" s="3">
         <v>42500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>82200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1902500</v>
+        <v>2109300</v>
       </c>
       <c r="E61" s="3">
-        <v>1786600</v>
+        <v>1933900</v>
       </c>
       <c r="F61" s="3">
-        <v>1425800</v>
+        <v>1816100</v>
       </c>
       <c r="G61" s="3">
-        <v>886500</v>
+        <v>1449300</v>
       </c>
       <c r="H61" s="3">
-        <v>871300</v>
+        <v>901100</v>
       </c>
       <c r="I61" s="3">
-        <v>470600</v>
+        <v>885600</v>
       </c>
       <c r="J61" s="3">
+        <v>478400</v>
+      </c>
+      <c r="K61" s="3">
         <v>470200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>393300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>402200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>387900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>198400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>202200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>409900</v>
+        <v>402000</v>
       </c>
       <c r="E62" s="3">
-        <v>453100</v>
+        <v>416600</v>
       </c>
       <c r="F62" s="3">
-        <v>356300</v>
+        <v>460600</v>
       </c>
       <c r="G62" s="3">
-        <v>255400</v>
+        <v>362200</v>
       </c>
       <c r="H62" s="3">
-        <v>297100</v>
+        <v>259600</v>
       </c>
       <c r="I62" s="3">
-        <v>222100</v>
+        <v>302000</v>
       </c>
       <c r="J62" s="3">
+        <v>225800</v>
+      </c>
+      <c r="K62" s="3">
         <v>186600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>184800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>133700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>139600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>143000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2766300</v>
+        <v>2800300</v>
       </c>
       <c r="E66" s="3">
-        <v>2361400</v>
+        <v>2811800</v>
       </c>
       <c r="F66" s="3">
-        <v>2055600</v>
+        <v>2400300</v>
       </c>
       <c r="G66" s="3">
-        <v>1205200</v>
+        <v>2089400</v>
       </c>
       <c r="H66" s="3">
-        <v>1231000</v>
+        <v>1225100</v>
       </c>
       <c r="I66" s="3">
-        <v>777800</v>
+        <v>1251300</v>
       </c>
       <c r="J66" s="3">
+        <v>790600</v>
+      </c>
+      <c r="K66" s="3">
         <v>700400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>662900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>642000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>613900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>370600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>258300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1237700</v>
+        <v>1208100</v>
       </c>
       <c r="E72" s="3">
-        <v>1271500</v>
+        <v>1258100</v>
       </c>
       <c r="F72" s="3">
-        <v>459200</v>
+        <v>1292500</v>
       </c>
       <c r="G72" s="3">
-        <v>267000</v>
+        <v>466800</v>
       </c>
       <c r="H72" s="3">
-        <v>90500</v>
+        <v>271400</v>
       </c>
       <c r="I72" s="3">
-        <v>-116800</v>
+        <v>92000</v>
       </c>
       <c r="J72" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-287400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-418300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-504100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-468600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-492900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-673300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3980700</v>
+        <v>3899600</v>
       </c>
       <c r="E76" s="3">
-        <v>3866700</v>
+        <v>4046200</v>
       </c>
       <c r="F76" s="3">
-        <v>2849900</v>
+        <v>3930400</v>
       </c>
       <c r="G76" s="3">
-        <v>2287300</v>
+        <v>2896900</v>
       </c>
       <c r="H76" s="3">
-        <v>1814300</v>
+        <v>2325000</v>
       </c>
       <c r="I76" s="3">
-        <v>1553300</v>
+        <v>1844200</v>
       </c>
       <c r="J76" s="3">
+        <v>1578900</v>
+      </c>
+      <c r="K76" s="3">
         <v>1416400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1388400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1279600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1286500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1140300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>698500</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>113200</v>
+        <v>101000</v>
       </c>
       <c r="E81" s="3">
-        <v>952300</v>
+        <v>115100</v>
       </c>
       <c r="F81" s="3">
-        <v>312500</v>
+        <v>968000</v>
       </c>
       <c r="G81" s="3">
-        <v>277800</v>
+        <v>317600</v>
       </c>
       <c r="H81" s="3">
-        <v>338200</v>
+        <v>282400</v>
       </c>
       <c r="I81" s="3">
-        <v>260100</v>
+        <v>343700</v>
       </c>
       <c r="J81" s="3">
+        <v>264300</v>
+      </c>
+      <c r="K81" s="3">
         <v>203100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>145200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>55100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>111600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>112700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117100</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,31 +3687,32 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
-        <v>800</v>
-      </c>
       <c r="G83" s="3">
+        <v>900</v>
+      </c>
+      <c r="H83" s="3">
         <v>700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3523,17 +3721,20 @@
         <v>500</v>
       </c>
       <c r="M83" s="3">
+        <v>500</v>
+      </c>
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>201700</v>
+        <v>231400</v>
       </c>
       <c r="E89" s="3">
-        <v>190700</v>
+        <v>205100</v>
       </c>
       <c r="F89" s="3">
-        <v>177600</v>
+        <v>193800</v>
       </c>
       <c r="G89" s="3">
-        <v>133400</v>
+        <v>180600</v>
       </c>
       <c r="H89" s="3">
-        <v>114800</v>
+        <v>135600</v>
       </c>
       <c r="I89" s="3">
-        <v>115400</v>
+        <v>116700</v>
       </c>
       <c r="J89" s="3">
+        <v>117300</v>
+      </c>
+      <c r="K89" s="3">
         <v>116300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>120000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>72900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>87400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>86000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-194800</v>
+        <v>-97000</v>
       </c>
       <c r="E91" s="3">
-        <v>-72500</v>
+        <v>-198000</v>
       </c>
       <c r="F91" s="3">
-        <v>-47500</v>
+        <v>-73700</v>
       </c>
       <c r="G91" s="3">
-        <v>-22200</v>
+        <v>-48200</v>
       </c>
       <c r="H91" s="3">
-        <v>-25100</v>
+        <v>-22500</v>
       </c>
       <c r="I91" s="3">
-        <v>-60800</v>
+        <v>-25500</v>
       </c>
       <c r="J91" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-14200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37300</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-557300</v>
+        <v>-94700</v>
       </c>
       <c r="E94" s="3">
-        <v>-745500</v>
+        <v>-566500</v>
       </c>
       <c r="F94" s="3">
-        <v>-775600</v>
+        <v>-757800</v>
       </c>
       <c r="G94" s="3">
-        <v>-636900</v>
+        <v>-788400</v>
       </c>
       <c r="H94" s="3">
-        <v>69700</v>
+        <v>-647400</v>
       </c>
       <c r="I94" s="3">
-        <v>-172900</v>
+        <v>70800</v>
       </c>
       <c r="J94" s="3">
+        <v>-175800</v>
+      </c>
+      <c r="K94" s="3">
         <v>8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-195200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-73900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-147100</v>
+        <v>-150700</v>
       </c>
       <c r="E96" s="3">
-        <v>-138900</v>
+        <v>-149500</v>
       </c>
       <c r="F96" s="3">
-        <v>-118500</v>
+        <v>-141200</v>
       </c>
       <c r="G96" s="3">
-        <v>-109500</v>
+        <v>-120500</v>
       </c>
       <c r="H96" s="3">
-        <v>-91000</v>
+        <v>-111300</v>
       </c>
       <c r="I96" s="3">
-        <v>-89200</v>
+        <v>-92500</v>
       </c>
       <c r="J96" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-82200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-81300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-81000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-69500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-70600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-29000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>156000</v>
+        <v>-150100</v>
       </c>
       <c r="E100" s="3">
-        <v>242400</v>
+        <v>158600</v>
       </c>
       <c r="F100" s="3">
-        <v>987400</v>
+        <v>246400</v>
       </c>
       <c r="G100" s="3">
-        <v>249700</v>
+        <v>1003700</v>
       </c>
       <c r="H100" s="3">
-        <v>235700</v>
+        <v>253900</v>
       </c>
       <c r="I100" s="3">
-        <v>-76500</v>
+        <v>239600</v>
       </c>
       <c r="J100" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-29100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-71200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>124800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-72200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5100</v>
+        <v>-700</v>
       </c>
       <c r="E101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
-        <v>-2200</v>
-      </c>
       <c r="G101" s="3">
-        <v>-7600</v>
+        <v>-2300</v>
       </c>
       <c r="H101" s="3">
-        <v>8200</v>
+        <v>-7700</v>
       </c>
       <c r="I101" s="3">
-        <v>5200</v>
+        <v>8300</v>
       </c>
       <c r="J101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1600</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-194400</v>
+        <v>-14000</v>
       </c>
       <c r="E102" s="3">
-        <v>-311700</v>
+        <v>-197600</v>
       </c>
       <c r="F102" s="3">
-        <v>387200</v>
+        <v>-316900</v>
       </c>
       <c r="G102" s="3">
-        <v>-261400</v>
+        <v>393600</v>
       </c>
       <c r="H102" s="3">
-        <v>428400</v>
+        <v>-265700</v>
       </c>
       <c r="I102" s="3">
-        <v>-128800</v>
+        <v>435400</v>
       </c>
       <c r="J102" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="K102" s="3">
         <v>92400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>385200</v>
+        <v>379900</v>
       </c>
       <c r="E8" s="3">
-        <v>336700</v>
+        <v>332000</v>
       </c>
       <c r="F8" s="3">
-        <v>290800</v>
+        <v>286800</v>
       </c>
       <c r="G8" s="3">
-        <v>251400</v>
+        <v>247900</v>
       </c>
       <c r="H8" s="3">
-        <v>202200</v>
+        <v>199400</v>
       </c>
       <c r="I8" s="3">
-        <v>182900</v>
+        <v>180400</v>
       </c>
       <c r="J8" s="3">
-        <v>180800</v>
+        <v>178300</v>
       </c>
       <c r="K8" s="3">
         <v>162400</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>63600</v>
+        <v>62700</v>
       </c>
       <c r="E9" s="3">
-        <v>55600</v>
+        <v>54800</v>
       </c>
       <c r="F9" s="3">
-        <v>44900</v>
+        <v>44300</v>
       </c>
       <c r="G9" s="3">
-        <v>34900</v>
+        <v>34400</v>
       </c>
       <c r="H9" s="3">
-        <v>26100</v>
+        <v>25800</v>
       </c>
       <c r="I9" s="3">
-        <v>22900</v>
+        <v>22500</v>
       </c>
       <c r="J9" s="3">
-        <v>23200</v>
+        <v>22800</v>
       </c>
       <c r="K9" s="3">
         <v>5600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>321600</v>
+        <v>317200</v>
       </c>
       <c r="E10" s="3">
-        <v>281100</v>
+        <v>277200</v>
       </c>
       <c r="F10" s="3">
-        <v>245800</v>
+        <v>242400</v>
       </c>
       <c r="G10" s="3">
-        <v>216500</v>
+        <v>213600</v>
       </c>
       <c r="H10" s="3">
-        <v>176100</v>
+        <v>173700</v>
       </c>
       <c r="I10" s="3">
-        <v>160000</v>
+        <v>157800</v>
       </c>
       <c r="J10" s="3">
-        <v>157700</v>
+        <v>155500</v>
       </c>
       <c r="K10" s="3">
         <v>156900</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="J14" s="3">
         <v>500</v>
@@ -1024,7 +1024,7 @@
         <v>1000</v>
       </c>
       <c r="G15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>148400</v>
+        <v>146300</v>
       </c>
       <c r="E17" s="3">
-        <v>114100</v>
+        <v>112500</v>
       </c>
       <c r="F17" s="3">
-        <v>103100</v>
+        <v>101700</v>
       </c>
       <c r="G17" s="3">
-        <v>81500</v>
+        <v>80400</v>
       </c>
       <c r="H17" s="3">
-        <v>66300</v>
+        <v>65300</v>
       </c>
       <c r="I17" s="3">
-        <v>58400</v>
+        <v>57600</v>
       </c>
       <c r="J17" s="3">
-        <v>62400</v>
+        <v>61500</v>
       </c>
       <c r="K17" s="3">
         <v>40400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>236800</v>
+        <v>233600</v>
       </c>
       <c r="E18" s="3">
-        <v>222600</v>
+        <v>219500</v>
       </c>
       <c r="F18" s="3">
-        <v>187700</v>
+        <v>185100</v>
       </c>
       <c r="G18" s="3">
-        <v>169900</v>
+        <v>167500</v>
       </c>
       <c r="H18" s="3">
-        <v>136000</v>
+        <v>134100</v>
       </c>
       <c r="I18" s="3">
-        <v>124500</v>
+        <v>122800</v>
       </c>
       <c r="J18" s="3">
-        <v>118500</v>
+        <v>116800</v>
       </c>
       <c r="K18" s="3">
         <v>122100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-141500</v>
+        <v>-139500</v>
       </c>
       <c r="E20" s="3">
-        <v>-154500</v>
+        <v>-152300</v>
       </c>
       <c r="F20" s="3">
-        <v>958400</v>
+        <v>945100</v>
       </c>
       <c r="G20" s="3">
-        <v>198900</v>
+        <v>196100</v>
       </c>
       <c r="H20" s="3">
-        <v>178000</v>
+        <v>175600</v>
       </c>
       <c r="I20" s="3">
-        <v>258300</v>
+        <v>254700</v>
       </c>
       <c r="J20" s="3">
-        <v>155800</v>
+        <v>153700</v>
       </c>
       <c r="K20" s="3">
         <v>116600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>96300</v>
+        <v>94900</v>
       </c>
       <c r="E21" s="3">
-        <v>69300</v>
+        <v>68300</v>
       </c>
       <c r="F21" s="3">
-        <v>1147000</v>
+        <v>1131100</v>
       </c>
       <c r="G21" s="3">
-        <v>369600</v>
+        <v>364500</v>
       </c>
       <c r="H21" s="3">
-        <v>314700</v>
+        <v>310300</v>
       </c>
       <c r="I21" s="3">
-        <v>383000</v>
+        <v>377700</v>
       </c>
       <c r="J21" s="3">
-        <v>274500</v>
+        <v>270700</v>
       </c>
       <c r="K21" s="3">
         <v>239200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>95300</v>
+        <v>94000</v>
       </c>
       <c r="E23" s="3">
-        <v>68100</v>
+        <v>67200</v>
       </c>
       <c r="F23" s="3">
-        <v>1146100</v>
+        <v>1130200</v>
       </c>
       <c r="G23" s="3">
-        <v>368800</v>
+        <v>363700</v>
       </c>
       <c r="H23" s="3">
-        <v>314000</v>
+        <v>309700</v>
       </c>
       <c r="I23" s="3">
-        <v>382800</v>
+        <v>377500</v>
       </c>
       <c r="J23" s="3">
-        <v>274300</v>
+        <v>270500</v>
       </c>
       <c r="K23" s="3">
         <v>238700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="E24" s="3">
-        <v>-47000</v>
+        <v>-46400</v>
       </c>
       <c r="F24" s="3">
-        <v>177800</v>
+        <v>175300</v>
       </c>
       <c r="G24" s="3">
-        <v>51100</v>
+        <v>50400</v>
       </c>
       <c r="H24" s="3">
-        <v>31500</v>
+        <v>31100</v>
       </c>
       <c r="I24" s="3">
-        <v>38900</v>
+        <v>38400</v>
       </c>
       <c r="J24" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="K24" s="3">
         <v>34600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>102300</v>
+        <v>100900</v>
       </c>
       <c r="E26" s="3">
-        <v>115200</v>
+        <v>113600</v>
       </c>
       <c r="F26" s="3">
-        <v>968300</v>
+        <v>954900</v>
       </c>
       <c r="G26" s="3">
-        <v>317700</v>
+        <v>313300</v>
       </c>
       <c r="H26" s="3">
-        <v>282500</v>
+        <v>278600</v>
       </c>
       <c r="I26" s="3">
-        <v>343900</v>
+        <v>339100</v>
       </c>
       <c r="J26" s="3">
-        <v>264400</v>
+        <v>260700</v>
       </c>
       <c r="K26" s="3">
         <v>204100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>101000</v>
+        <v>99600</v>
       </c>
       <c r="E27" s="3">
-        <v>115100</v>
+        <v>113500</v>
       </c>
       <c r="F27" s="3">
-        <v>968000</v>
+        <v>954600</v>
       </c>
       <c r="G27" s="3">
-        <v>317600</v>
+        <v>313200</v>
       </c>
       <c r="H27" s="3">
-        <v>282400</v>
+        <v>278400</v>
       </c>
       <c r="I27" s="3">
-        <v>343700</v>
+        <v>339000</v>
       </c>
       <c r="J27" s="3">
-        <v>264300</v>
+        <v>260700</v>
       </c>
       <c r="K27" s="3">
         <v>203100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>141500</v>
+        <v>139500</v>
       </c>
       <c r="E32" s="3">
-        <v>154500</v>
+        <v>152300</v>
       </c>
       <c r="F32" s="3">
-        <v>-958400</v>
+        <v>-945100</v>
       </c>
       <c r="G32" s="3">
-        <v>-198900</v>
+        <v>-196100</v>
       </c>
       <c r="H32" s="3">
-        <v>-178000</v>
+        <v>-175600</v>
       </c>
       <c r="I32" s="3">
-        <v>-258300</v>
+        <v>-254700</v>
       </c>
       <c r="J32" s="3">
-        <v>-155800</v>
+        <v>-153700</v>
       </c>
       <c r="K32" s="3">
         <v>-116600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>101000</v>
+        <v>99600</v>
       </c>
       <c r="E33" s="3">
-        <v>115100</v>
+        <v>113500</v>
       </c>
       <c r="F33" s="3">
-        <v>968000</v>
+        <v>954600</v>
       </c>
       <c r="G33" s="3">
-        <v>317600</v>
+        <v>313200</v>
       </c>
       <c r="H33" s="3">
-        <v>282400</v>
+        <v>278400</v>
       </c>
       <c r="I33" s="3">
-        <v>343700</v>
+        <v>339000</v>
       </c>
       <c r="J33" s="3">
-        <v>264300</v>
+        <v>260700</v>
       </c>
       <c r="K33" s="3">
         <v>203100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>101000</v>
+        <v>99600</v>
       </c>
       <c r="E35" s="3">
-        <v>115100</v>
+        <v>113500</v>
       </c>
       <c r="F35" s="3">
-        <v>968000</v>
+        <v>954600</v>
       </c>
       <c r="G35" s="3">
-        <v>317600</v>
+        <v>313200</v>
       </c>
       <c r="H35" s="3">
-        <v>282400</v>
+        <v>278400</v>
       </c>
       <c r="I35" s="3">
-        <v>343700</v>
+        <v>339000</v>
       </c>
       <c r="J35" s="3">
-        <v>264300</v>
+        <v>260700</v>
       </c>
       <c r="K35" s="3">
         <v>203100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>85500</v>
+        <v>84300</v>
       </c>
       <c r="E41" s="3">
-        <v>93900</v>
+        <v>92600</v>
       </c>
       <c r="F41" s="3">
-        <v>297000</v>
+        <v>292900</v>
       </c>
       <c r="G41" s="3">
-        <v>577100</v>
+        <v>569100</v>
       </c>
       <c r="H41" s="3">
-        <v>183600</v>
+        <v>181100</v>
       </c>
       <c r="I41" s="3">
-        <v>395300</v>
+        <v>389900</v>
       </c>
       <c r="J41" s="3">
-        <v>41100</v>
+        <v>40500</v>
       </c>
       <c r="K41" s="3">
         <v>79500</v>
@@ -2041,22 +2041,22 @@
         <v>300</v>
       </c>
       <c r="E42" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="F42" s="3">
         <v>400</v>
       </c>
       <c r="G42" s="3">
-        <v>37200</v>
+        <v>36700</v>
       </c>
       <c r="H42" s="3">
-        <v>37100</v>
+        <v>36600</v>
       </c>
       <c r="I42" s="3">
-        <v>91100</v>
+        <v>89800</v>
       </c>
       <c r="J42" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="K42" s="3">
         <v>99500</v>
@@ -2083,19 +2083,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9400</v>
+        <v>9300</v>
       </c>
       <c r="E43" s="3">
-        <v>61100</v>
+        <v>60200</v>
       </c>
       <c r="F43" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G43" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="H43" s="3">
-        <v>14600</v>
+        <v>14400</v>
       </c>
       <c r="I43" s="3">
         <v>3300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16900</v>
+        <v>16600</v>
       </c>
       <c r="E45" s="3">
-        <v>41300</v>
+        <v>40700</v>
       </c>
       <c r="F45" s="3">
-        <v>53100</v>
+        <v>52300</v>
       </c>
       <c r="G45" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="H45" s="3">
         <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>34900</v>
+        <v>34400</v>
       </c>
       <c r="J45" s="3">
-        <v>291200</v>
+        <v>287100</v>
       </c>
       <c r="K45" s="3">
         <v>2200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>112100</v>
+        <v>110600</v>
       </c>
       <c r="E46" s="3">
-        <v>202200</v>
+        <v>199400</v>
       </c>
       <c r="F46" s="3">
-        <v>359500</v>
+        <v>354600</v>
       </c>
       <c r="G46" s="3">
-        <v>625100</v>
+        <v>616400</v>
       </c>
       <c r="H46" s="3">
-        <v>237800</v>
+        <v>234500</v>
       </c>
       <c r="I46" s="3">
-        <v>524700</v>
+        <v>517400</v>
       </c>
       <c r="J46" s="3">
-        <v>344000</v>
+        <v>339200</v>
       </c>
       <c r="K46" s="3">
         <v>182200</v>
@@ -2269,7 +2269,7 @@
         <v>200</v>
       </c>
       <c r="F47" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="G47" s="3">
         <v>300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6511500</v>
+        <v>6421300</v>
       </c>
       <c r="E48" s="3">
-        <v>6535300</v>
+        <v>6444900</v>
       </c>
       <c r="F48" s="3">
-        <v>5892400</v>
+        <v>5810900</v>
       </c>
       <c r="G48" s="3">
-        <v>4329600</v>
+        <v>4269700</v>
       </c>
       <c r="H48" s="3">
-        <v>3295900</v>
+        <v>3250300</v>
       </c>
       <c r="I48" s="3">
-        <v>2531600</v>
+        <v>2496500</v>
       </c>
       <c r="J48" s="3">
-        <v>2020800</v>
+        <v>1992800</v>
       </c>
       <c r="K48" s="3">
         <v>1929400</v>
@@ -2488,22 +2488,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>76200</v>
+        <v>75100</v>
       </c>
       <c r="E52" s="3">
-        <v>120400</v>
+        <v>118700</v>
       </c>
       <c r="F52" s="3">
-        <v>70800</v>
+        <v>69800</v>
       </c>
       <c r="G52" s="3">
-        <v>31300</v>
+        <v>30900</v>
       </c>
       <c r="H52" s="3">
-        <v>16300</v>
+        <v>16100</v>
       </c>
       <c r="I52" s="3">
-        <v>39200</v>
+        <v>38600</v>
       </c>
       <c r="J52" s="3">
         <v>4700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6700000</v>
+        <v>6607200</v>
       </c>
       <c r="E54" s="3">
-        <v>6858100</v>
+        <v>6763200</v>
       </c>
       <c r="F54" s="3">
-        <v>6330700</v>
+        <v>6243100</v>
       </c>
       <c r="G54" s="3">
-        <v>4986300</v>
+        <v>4917300</v>
       </c>
       <c r="H54" s="3">
-        <v>3550100</v>
+        <v>3500900</v>
       </c>
       <c r="I54" s="3">
-        <v>3095400</v>
+        <v>3052600</v>
       </c>
       <c r="J54" s="3">
-        <v>2369500</v>
+        <v>2336700</v>
       </c>
       <c r="K54" s="3">
         <v>2116800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="E57" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="F57" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="G57" s="3">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="H57" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="I57" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="J57" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="K57" s="3">
         <v>4100</v>
@@ -2706,16 +2706,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>181000</v>
+        <v>178500</v>
       </c>
       <c r="E58" s="3">
-        <v>333900</v>
+        <v>329300</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>185300</v>
+        <v>182700</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>24100</v>
+        <v>23700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>94700</v>
+        <v>93400</v>
       </c>
       <c r="E59" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F59" s="3">
         <v>115500</v>
       </c>
-      <c r="F59" s="3">
-        <v>117100</v>
-      </c>
       <c r="G59" s="3">
-        <v>83800</v>
+        <v>82600</v>
       </c>
       <c r="H59" s="3">
-        <v>57400</v>
+        <v>56600</v>
       </c>
       <c r="I59" s="3">
-        <v>58600</v>
+        <v>57800</v>
       </c>
       <c r="J59" s="3">
-        <v>57300</v>
+        <v>56500</v>
       </c>
       <c r="K59" s="3">
         <v>38400</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>284100</v>
+        <v>280200</v>
       </c>
       <c r="E60" s="3">
-        <v>457700</v>
+        <v>451300</v>
       </c>
       <c r="F60" s="3">
-        <v>121500</v>
+        <v>119800</v>
       </c>
       <c r="G60" s="3">
-        <v>276300</v>
+        <v>272500</v>
       </c>
       <c r="H60" s="3">
-        <v>62900</v>
+        <v>62000</v>
       </c>
       <c r="I60" s="3">
-        <v>62500</v>
+        <v>61700</v>
       </c>
       <c r="J60" s="3">
-        <v>85500</v>
+        <v>84400</v>
       </c>
       <c r="K60" s="3">
         <v>42500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2109300</v>
+        <v>2080100</v>
       </c>
       <c r="E61" s="3">
-        <v>1933900</v>
+        <v>1907100</v>
       </c>
       <c r="F61" s="3">
-        <v>1816100</v>
+        <v>1790900</v>
       </c>
       <c r="G61" s="3">
-        <v>1449300</v>
+        <v>1429200</v>
       </c>
       <c r="H61" s="3">
-        <v>901100</v>
+        <v>888700</v>
       </c>
       <c r="I61" s="3">
-        <v>885600</v>
+        <v>873400</v>
       </c>
       <c r="J61" s="3">
-        <v>478400</v>
+        <v>471700</v>
       </c>
       <c r="K61" s="3">
         <v>470200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>402000</v>
+        <v>396400</v>
       </c>
       <c r="E62" s="3">
-        <v>416600</v>
+        <v>410900</v>
       </c>
       <c r="F62" s="3">
-        <v>460600</v>
+        <v>454200</v>
       </c>
       <c r="G62" s="3">
-        <v>362200</v>
+        <v>357200</v>
       </c>
       <c r="H62" s="3">
-        <v>259600</v>
+        <v>256000</v>
       </c>
       <c r="I62" s="3">
-        <v>302000</v>
+        <v>297900</v>
       </c>
       <c r="J62" s="3">
-        <v>225800</v>
+        <v>222600</v>
       </c>
       <c r="K62" s="3">
         <v>186600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2800300</v>
+        <v>2761600</v>
       </c>
       <c r="E66" s="3">
-        <v>2811800</v>
+        <v>2772900</v>
       </c>
       <c r="F66" s="3">
-        <v>2400300</v>
+        <v>2367000</v>
       </c>
       <c r="G66" s="3">
-        <v>2089400</v>
+        <v>2060500</v>
       </c>
       <c r="H66" s="3">
-        <v>1225100</v>
+        <v>1208100</v>
       </c>
       <c r="I66" s="3">
-        <v>1251300</v>
+        <v>1234000</v>
       </c>
       <c r="J66" s="3">
-        <v>790600</v>
+        <v>779600</v>
       </c>
       <c r="K66" s="3">
         <v>700400</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1208100</v>
+        <v>1191300</v>
       </c>
       <c r="E72" s="3">
-        <v>1258100</v>
+        <v>1240700</v>
       </c>
       <c r="F72" s="3">
-        <v>1292500</v>
+        <v>1274600</v>
       </c>
       <c r="G72" s="3">
-        <v>466800</v>
+        <v>460300</v>
       </c>
       <c r="H72" s="3">
-        <v>271400</v>
+        <v>267600</v>
       </c>
       <c r="I72" s="3">
-        <v>92000</v>
+        <v>90700</v>
       </c>
       <c r="J72" s="3">
-        <v>-118700</v>
+        <v>-117100</v>
       </c>
       <c r="K72" s="3">
         <v>-287400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3899600</v>
+        <v>3845600</v>
       </c>
       <c r="E76" s="3">
-        <v>4046200</v>
+        <v>3990200</v>
       </c>
       <c r="F76" s="3">
-        <v>3930400</v>
+        <v>3876000</v>
       </c>
       <c r="G76" s="3">
-        <v>2896900</v>
+        <v>2856800</v>
       </c>
       <c r="H76" s="3">
-        <v>2325000</v>
+        <v>2292800</v>
       </c>
       <c r="I76" s="3">
-        <v>1844200</v>
+        <v>1818600</v>
       </c>
       <c r="J76" s="3">
-        <v>1578900</v>
+        <v>1557100</v>
       </c>
       <c r="K76" s="3">
         <v>1416400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>101000</v>
+        <v>99600</v>
       </c>
       <c r="E81" s="3">
-        <v>115100</v>
+        <v>113500</v>
       </c>
       <c r="F81" s="3">
-        <v>968000</v>
+        <v>954600</v>
       </c>
       <c r="G81" s="3">
-        <v>317600</v>
+        <v>313200</v>
       </c>
       <c r="H81" s="3">
-        <v>282400</v>
+        <v>278400</v>
       </c>
       <c r="I81" s="3">
-        <v>343700</v>
+        <v>339000</v>
       </c>
       <c r="J81" s="3">
-        <v>264300</v>
+        <v>260700</v>
       </c>
       <c r="K81" s="3">
         <v>203100</v>
@@ -3703,7 +3703,7 @@
         <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>231400</v>
+        <v>228200</v>
       </c>
       <c r="E89" s="3">
-        <v>205100</v>
+        <v>202200</v>
       </c>
       <c r="F89" s="3">
-        <v>193800</v>
+        <v>191100</v>
       </c>
       <c r="G89" s="3">
-        <v>180600</v>
+        <v>178100</v>
       </c>
       <c r="H89" s="3">
-        <v>135600</v>
+        <v>133700</v>
       </c>
       <c r="I89" s="3">
-        <v>116700</v>
+        <v>115100</v>
       </c>
       <c r="J89" s="3">
-        <v>117300</v>
+        <v>115600</v>
       </c>
       <c r="K89" s="3">
         <v>116300</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-97000</v>
+        <v>-95600</v>
       </c>
       <c r="E91" s="3">
-        <v>-198000</v>
+        <v>-195300</v>
       </c>
       <c r="F91" s="3">
-        <v>-73700</v>
+        <v>-72700</v>
       </c>
       <c r="G91" s="3">
-        <v>-48200</v>
+        <v>-47600</v>
       </c>
       <c r="H91" s="3">
-        <v>-22500</v>
+        <v>-22200</v>
       </c>
       <c r="I91" s="3">
-        <v>-25500</v>
+        <v>-25200</v>
       </c>
       <c r="J91" s="3">
-        <v>-61800</v>
+        <v>-61000</v>
       </c>
       <c r="K91" s="3">
         <v>-14200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-94700</v>
+        <v>-93400</v>
       </c>
       <c r="E94" s="3">
-        <v>-566500</v>
+        <v>-558600</v>
       </c>
       <c r="F94" s="3">
-        <v>-757800</v>
+        <v>-747300</v>
       </c>
       <c r="G94" s="3">
-        <v>-788400</v>
+        <v>-777500</v>
       </c>
       <c r="H94" s="3">
-        <v>-647400</v>
+        <v>-638500</v>
       </c>
       <c r="I94" s="3">
-        <v>70800</v>
+        <v>69900</v>
       </c>
       <c r="J94" s="3">
-        <v>-175800</v>
+        <v>-173300</v>
       </c>
       <c r="K94" s="3">
         <v>8600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-150700</v>
+        <v>-148600</v>
       </c>
       <c r="E96" s="3">
-        <v>-149500</v>
+        <v>-147400</v>
       </c>
       <c r="F96" s="3">
-        <v>-141200</v>
+        <v>-139300</v>
       </c>
       <c r="G96" s="3">
-        <v>-120500</v>
+        <v>-118800</v>
       </c>
       <c r="H96" s="3">
-        <v>-111300</v>
+        <v>-109800</v>
       </c>
       <c r="I96" s="3">
-        <v>-92500</v>
+        <v>-91200</v>
       </c>
       <c r="J96" s="3">
-        <v>-90600</v>
+        <v>-89400</v>
       </c>
       <c r="K96" s="3">
         <v>-82200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-150100</v>
+        <v>-148000</v>
       </c>
       <c r="E100" s="3">
-        <v>158600</v>
+        <v>156400</v>
       </c>
       <c r="F100" s="3">
-        <v>246400</v>
+        <v>243000</v>
       </c>
       <c r="G100" s="3">
-        <v>1003700</v>
+        <v>989800</v>
       </c>
       <c r="H100" s="3">
-        <v>253900</v>
+        <v>250300</v>
       </c>
       <c r="I100" s="3">
-        <v>239600</v>
+        <v>236300</v>
       </c>
       <c r="J100" s="3">
-        <v>-77800</v>
+        <v>-76700</v>
       </c>
       <c r="K100" s="3">
         <v>-29100</v>
@@ -4452,7 +4452,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="E101" s="3">
         <v>5200</v>
@@ -4464,10 +4464,10 @@
         <v>-2300</v>
       </c>
       <c r="H101" s="3">
-        <v>-7700</v>
+        <v>-7600</v>
       </c>
       <c r="I101" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="J101" s="3">
         <v>5300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-14000</v>
+        <v>-13800</v>
       </c>
       <c r="E102" s="3">
-        <v>-197600</v>
+        <v>-194900</v>
       </c>
       <c r="F102" s="3">
-        <v>-316900</v>
+        <v>-312500</v>
       </c>
       <c r="G102" s="3">
-        <v>393600</v>
+        <v>388100</v>
       </c>
       <c r="H102" s="3">
-        <v>-265700</v>
+        <v>-262000</v>
       </c>
       <c r="I102" s="3">
-        <v>435400</v>
+        <v>429400</v>
       </c>
       <c r="J102" s="3">
-        <v>-130900</v>
+        <v>-129100</v>
       </c>
       <c r="K102" s="3">
         <v>92400</v>

--- a/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>379900</v>
+        <v>383700</v>
       </c>
       <c r="E8" s="3">
-        <v>332000</v>
+        <v>335400</v>
       </c>
       <c r="F8" s="3">
-        <v>286800</v>
+        <v>289700</v>
       </c>
       <c r="G8" s="3">
-        <v>247900</v>
+        <v>250400</v>
       </c>
       <c r="H8" s="3">
-        <v>199400</v>
+        <v>201500</v>
       </c>
       <c r="I8" s="3">
-        <v>180400</v>
+        <v>182200</v>
       </c>
       <c r="J8" s="3">
-        <v>178300</v>
+        <v>180100</v>
       </c>
       <c r="K8" s="3">
         <v>162400</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>62700</v>
+        <v>63300</v>
       </c>
       <c r="E9" s="3">
-        <v>54800</v>
+        <v>55400</v>
       </c>
       <c r="F9" s="3">
-        <v>44300</v>
+        <v>44800</v>
       </c>
       <c r="G9" s="3">
-        <v>34400</v>
+        <v>34700</v>
       </c>
       <c r="H9" s="3">
-        <v>25800</v>
+        <v>26000</v>
       </c>
       <c r="I9" s="3">
-        <v>22500</v>
+        <v>22800</v>
       </c>
       <c r="J9" s="3">
-        <v>22800</v>
+        <v>23100</v>
       </c>
       <c r="K9" s="3">
         <v>5600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>317200</v>
+        <v>320400</v>
       </c>
       <c r="E10" s="3">
-        <v>277200</v>
+        <v>280000</v>
       </c>
       <c r="F10" s="3">
-        <v>242400</v>
+        <v>244900</v>
       </c>
       <c r="G10" s="3">
-        <v>213600</v>
+        <v>215700</v>
       </c>
       <c r="H10" s="3">
-        <v>173700</v>
+        <v>175400</v>
       </c>
       <c r="I10" s="3">
-        <v>157800</v>
+        <v>159400</v>
       </c>
       <c r="J10" s="3">
-        <v>155500</v>
+        <v>157000</v>
       </c>
       <c r="K10" s="3">
         <v>156900</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="J14" s="3">
         <v>500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>146300</v>
+        <v>147800</v>
       </c>
       <c r="E17" s="3">
-        <v>112500</v>
+        <v>113700</v>
       </c>
       <c r="F17" s="3">
-        <v>101700</v>
+        <v>102700</v>
       </c>
       <c r="G17" s="3">
-        <v>80400</v>
+        <v>81200</v>
       </c>
       <c r="H17" s="3">
-        <v>65300</v>
+        <v>66000</v>
       </c>
       <c r="I17" s="3">
-        <v>57600</v>
+        <v>58200</v>
       </c>
       <c r="J17" s="3">
-        <v>61500</v>
+        <v>62100</v>
       </c>
       <c r="K17" s="3">
         <v>40400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>233600</v>
+        <v>235900</v>
       </c>
       <c r="E18" s="3">
-        <v>219500</v>
+        <v>221700</v>
       </c>
       <c r="F18" s="3">
-        <v>185100</v>
+        <v>186900</v>
       </c>
       <c r="G18" s="3">
-        <v>167500</v>
+        <v>169200</v>
       </c>
       <c r="H18" s="3">
-        <v>134100</v>
+        <v>135500</v>
       </c>
       <c r="I18" s="3">
-        <v>122800</v>
+        <v>124000</v>
       </c>
       <c r="J18" s="3">
-        <v>116800</v>
+        <v>118000</v>
       </c>
       <c r="K18" s="3">
         <v>122100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-139500</v>
+        <v>-140900</v>
       </c>
       <c r="E20" s="3">
-        <v>-152300</v>
+        <v>-153900</v>
       </c>
       <c r="F20" s="3">
-        <v>945100</v>
+        <v>954700</v>
       </c>
       <c r="G20" s="3">
-        <v>196100</v>
+        <v>198100</v>
       </c>
       <c r="H20" s="3">
-        <v>175600</v>
+        <v>177300</v>
       </c>
       <c r="I20" s="3">
-        <v>254700</v>
+        <v>257300</v>
       </c>
       <c r="J20" s="3">
-        <v>153700</v>
+        <v>155200</v>
       </c>
       <c r="K20" s="3">
         <v>116600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>94900</v>
+        <v>95900</v>
       </c>
       <c r="E21" s="3">
-        <v>68300</v>
+        <v>69000</v>
       </c>
       <c r="F21" s="3">
-        <v>1131100</v>
+        <v>1142600</v>
       </c>
       <c r="G21" s="3">
-        <v>364500</v>
+        <v>368200</v>
       </c>
       <c r="H21" s="3">
-        <v>310300</v>
+        <v>313500</v>
       </c>
       <c r="I21" s="3">
-        <v>377700</v>
+        <v>381500</v>
       </c>
       <c r="J21" s="3">
-        <v>270700</v>
+        <v>273500</v>
       </c>
       <c r="K21" s="3">
         <v>239200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>94000</v>
+        <v>95000</v>
       </c>
       <c r="E23" s="3">
-        <v>67200</v>
+        <v>67800</v>
       </c>
       <c r="F23" s="3">
-        <v>1130200</v>
+        <v>1141600</v>
       </c>
       <c r="G23" s="3">
-        <v>363700</v>
+        <v>367300</v>
       </c>
       <c r="H23" s="3">
-        <v>309700</v>
+        <v>312800</v>
       </c>
       <c r="I23" s="3">
-        <v>377500</v>
+        <v>381300</v>
       </c>
       <c r="J23" s="3">
-        <v>270500</v>
+        <v>273200</v>
       </c>
       <c r="K23" s="3">
         <v>238700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="E24" s="3">
-        <v>-46400</v>
+        <v>-46900</v>
       </c>
       <c r="F24" s="3">
-        <v>175300</v>
+        <v>177100</v>
       </c>
       <c r="G24" s="3">
-        <v>50400</v>
+        <v>50900</v>
       </c>
       <c r="H24" s="3">
-        <v>31100</v>
+        <v>31400</v>
       </c>
       <c r="I24" s="3">
-        <v>38400</v>
+        <v>38800</v>
       </c>
       <c r="J24" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="K24" s="3">
         <v>34600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100900</v>
+        <v>101900</v>
       </c>
       <c r="E26" s="3">
-        <v>113600</v>
+        <v>114700</v>
       </c>
       <c r="F26" s="3">
-        <v>954900</v>
+        <v>964500</v>
       </c>
       <c r="G26" s="3">
-        <v>313300</v>
+        <v>316500</v>
       </c>
       <c r="H26" s="3">
-        <v>278600</v>
+        <v>281400</v>
       </c>
       <c r="I26" s="3">
-        <v>339100</v>
+        <v>342600</v>
       </c>
       <c r="J26" s="3">
-        <v>260700</v>
+        <v>263300</v>
       </c>
       <c r="K26" s="3">
         <v>204100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>99600</v>
+        <v>100600</v>
       </c>
       <c r="E27" s="3">
-        <v>113500</v>
+        <v>114700</v>
       </c>
       <c r="F27" s="3">
-        <v>954600</v>
+        <v>964300</v>
       </c>
       <c r="G27" s="3">
-        <v>313200</v>
+        <v>316400</v>
       </c>
       <c r="H27" s="3">
-        <v>278400</v>
+        <v>281300</v>
       </c>
       <c r="I27" s="3">
-        <v>339000</v>
+        <v>342400</v>
       </c>
       <c r="J27" s="3">
-        <v>260700</v>
+        <v>263300</v>
       </c>
       <c r="K27" s="3">
         <v>203100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>139500</v>
+        <v>140900</v>
       </c>
       <c r="E32" s="3">
-        <v>152300</v>
+        <v>153900</v>
       </c>
       <c r="F32" s="3">
-        <v>-945100</v>
+        <v>-954700</v>
       </c>
       <c r="G32" s="3">
-        <v>-196100</v>
+        <v>-198100</v>
       </c>
       <c r="H32" s="3">
-        <v>-175600</v>
+        <v>-177300</v>
       </c>
       <c r="I32" s="3">
-        <v>-254700</v>
+        <v>-257300</v>
       </c>
       <c r="J32" s="3">
-        <v>-153700</v>
+        <v>-155200</v>
       </c>
       <c r="K32" s="3">
         <v>-116600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>99600</v>
+        <v>100600</v>
       </c>
       <c r="E33" s="3">
-        <v>113500</v>
+        <v>114700</v>
       </c>
       <c r="F33" s="3">
-        <v>954600</v>
+        <v>964300</v>
       </c>
       <c r="G33" s="3">
-        <v>313200</v>
+        <v>316400</v>
       </c>
       <c r="H33" s="3">
-        <v>278400</v>
+        <v>281300</v>
       </c>
       <c r="I33" s="3">
-        <v>339000</v>
+        <v>342400</v>
       </c>
       <c r="J33" s="3">
-        <v>260700</v>
+        <v>263300</v>
       </c>
       <c r="K33" s="3">
         <v>203100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>99600</v>
+        <v>100600</v>
       </c>
       <c r="E35" s="3">
-        <v>113500</v>
+        <v>114700</v>
       </c>
       <c r="F35" s="3">
-        <v>954600</v>
+        <v>964300</v>
       </c>
       <c r="G35" s="3">
-        <v>313200</v>
+        <v>316400</v>
       </c>
       <c r="H35" s="3">
-        <v>278400</v>
+        <v>281300</v>
       </c>
       <c r="I35" s="3">
-        <v>339000</v>
+        <v>342400</v>
       </c>
       <c r="J35" s="3">
-        <v>260700</v>
+        <v>263300</v>
       </c>
       <c r="K35" s="3">
         <v>203100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>84300</v>
+        <v>85200</v>
       </c>
       <c r="E41" s="3">
-        <v>92600</v>
+        <v>93600</v>
       </c>
       <c r="F41" s="3">
-        <v>292900</v>
+        <v>295900</v>
       </c>
       <c r="G41" s="3">
-        <v>569100</v>
+        <v>574900</v>
       </c>
       <c r="H41" s="3">
-        <v>181100</v>
+        <v>182900</v>
       </c>
       <c r="I41" s="3">
-        <v>389900</v>
+        <v>393800</v>
       </c>
       <c r="J41" s="3">
-        <v>40500</v>
+        <v>40900</v>
       </c>
       <c r="K41" s="3">
         <v>79500</v>
@@ -2041,22 +2041,22 @@
         <v>300</v>
       </c>
       <c r="E42" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="F42" s="3">
         <v>400</v>
       </c>
       <c r="G42" s="3">
-        <v>36700</v>
+        <v>37000</v>
       </c>
       <c r="H42" s="3">
-        <v>36600</v>
+        <v>36900</v>
       </c>
       <c r="I42" s="3">
-        <v>89800</v>
+        <v>90700</v>
       </c>
       <c r="J42" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="K42" s="3">
         <v>99500</v>
@@ -2083,19 +2083,19 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="E43" s="3">
-        <v>60200</v>
+        <v>60800</v>
       </c>
       <c r="F43" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G43" s="3">
         <v>5600</v>
       </c>
       <c r="H43" s="3">
-        <v>14400</v>
+        <v>14600</v>
       </c>
       <c r="I43" s="3">
         <v>3300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16600</v>
+        <v>16800</v>
       </c>
       <c r="E45" s="3">
-        <v>40700</v>
+        <v>41100</v>
       </c>
       <c r="F45" s="3">
-        <v>52300</v>
+        <v>52900</v>
       </c>
       <c r="G45" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="H45" s="3">
         <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>34400</v>
+        <v>34800</v>
       </c>
       <c r="J45" s="3">
-        <v>287100</v>
+        <v>290000</v>
       </c>
       <c r="K45" s="3">
         <v>2200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>110600</v>
+        <v>111700</v>
       </c>
       <c r="E46" s="3">
-        <v>199400</v>
+        <v>201400</v>
       </c>
       <c r="F46" s="3">
-        <v>354600</v>
+        <v>358100</v>
       </c>
       <c r="G46" s="3">
-        <v>616400</v>
+        <v>622600</v>
       </c>
       <c r="H46" s="3">
-        <v>234500</v>
+        <v>236900</v>
       </c>
       <c r="I46" s="3">
-        <v>517400</v>
+        <v>522600</v>
       </c>
       <c r="J46" s="3">
-        <v>339200</v>
+        <v>342700</v>
       </c>
       <c r="K46" s="3">
         <v>182200</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6421300</v>
+        <v>6486100</v>
       </c>
       <c r="E48" s="3">
-        <v>6444900</v>
+        <v>6509900</v>
       </c>
       <c r="F48" s="3">
-        <v>5810900</v>
+        <v>5869500</v>
       </c>
       <c r="G48" s="3">
-        <v>4269700</v>
+        <v>4312800</v>
       </c>
       <c r="H48" s="3">
-        <v>3250300</v>
+        <v>3283100</v>
       </c>
       <c r="I48" s="3">
-        <v>2496500</v>
+        <v>2521700</v>
       </c>
       <c r="J48" s="3">
-        <v>1992800</v>
+        <v>2012900</v>
       </c>
       <c r="K48" s="3">
         <v>1929400</v>
@@ -2488,22 +2488,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>75100</v>
+        <v>75900</v>
       </c>
       <c r="E52" s="3">
-        <v>118700</v>
+        <v>119900</v>
       </c>
       <c r="F52" s="3">
-        <v>69800</v>
+        <v>70500</v>
       </c>
       <c r="G52" s="3">
-        <v>30900</v>
+        <v>31200</v>
       </c>
       <c r="H52" s="3">
-        <v>16100</v>
+        <v>16300</v>
       </c>
       <c r="I52" s="3">
-        <v>38600</v>
+        <v>39000</v>
       </c>
       <c r="J52" s="3">
         <v>4700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6607200</v>
+        <v>6673900</v>
       </c>
       <c r="E54" s="3">
-        <v>6763200</v>
+        <v>6831400</v>
       </c>
       <c r="F54" s="3">
-        <v>6243100</v>
+        <v>6306000</v>
       </c>
       <c r="G54" s="3">
-        <v>4917300</v>
+        <v>4966900</v>
       </c>
       <c r="H54" s="3">
-        <v>3500900</v>
+        <v>3536200</v>
       </c>
       <c r="I54" s="3">
-        <v>3052600</v>
+        <v>3083400</v>
       </c>
       <c r="J54" s="3">
-        <v>2336700</v>
+        <v>2360300</v>
       </c>
       <c r="K54" s="3">
         <v>2116800</v>
@@ -2661,16 +2661,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="E57" s="3">
         <v>8200</v>
       </c>
       <c r="F57" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G57" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="H57" s="3">
         <v>5000</v>
@@ -2679,7 +2679,7 @@
         <v>3900</v>
       </c>
       <c r="J57" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="K57" s="3">
         <v>4100</v>
@@ -2706,16 +2706,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>178500</v>
+        <v>180300</v>
       </c>
       <c r="E58" s="3">
-        <v>329300</v>
+        <v>332600</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>182700</v>
+        <v>184500</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>23700</v>
+        <v>24000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>93400</v>
+        <v>94400</v>
       </c>
       <c r="E59" s="3">
-        <v>113900</v>
+        <v>115000</v>
       </c>
       <c r="F59" s="3">
-        <v>115500</v>
+        <v>116700</v>
       </c>
       <c r="G59" s="3">
-        <v>82600</v>
+        <v>83400</v>
       </c>
       <c r="H59" s="3">
-        <v>56600</v>
+        <v>57100</v>
       </c>
       <c r="I59" s="3">
-        <v>57800</v>
+        <v>58400</v>
       </c>
       <c r="J59" s="3">
-        <v>56500</v>
+        <v>57100</v>
       </c>
       <c r="K59" s="3">
         <v>38400</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>280200</v>
+        <v>283000</v>
       </c>
       <c r="E60" s="3">
-        <v>451300</v>
+        <v>455900</v>
       </c>
       <c r="F60" s="3">
-        <v>119800</v>
+        <v>121000</v>
       </c>
       <c r="G60" s="3">
-        <v>272500</v>
+        <v>275200</v>
       </c>
       <c r="H60" s="3">
-        <v>62000</v>
+        <v>62600</v>
       </c>
       <c r="I60" s="3">
-        <v>61700</v>
+        <v>62300</v>
       </c>
       <c r="J60" s="3">
-        <v>84400</v>
+        <v>85200</v>
       </c>
       <c r="K60" s="3">
         <v>42500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2080100</v>
+        <v>2101100</v>
       </c>
       <c r="E61" s="3">
-        <v>1907100</v>
+        <v>1926300</v>
       </c>
       <c r="F61" s="3">
-        <v>1790900</v>
+        <v>1809000</v>
       </c>
       <c r="G61" s="3">
-        <v>1429200</v>
+        <v>1443700</v>
       </c>
       <c r="H61" s="3">
-        <v>888700</v>
+        <v>897600</v>
       </c>
       <c r="I61" s="3">
-        <v>873400</v>
+        <v>882200</v>
       </c>
       <c r="J61" s="3">
-        <v>471700</v>
+        <v>476500</v>
       </c>
       <c r="K61" s="3">
         <v>470200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>396400</v>
+        <v>400400</v>
       </c>
       <c r="E62" s="3">
-        <v>410900</v>
+        <v>415000</v>
       </c>
       <c r="F62" s="3">
-        <v>454200</v>
+        <v>458800</v>
       </c>
       <c r="G62" s="3">
-        <v>357200</v>
+        <v>360800</v>
       </c>
       <c r="H62" s="3">
-        <v>256000</v>
+        <v>258600</v>
       </c>
       <c r="I62" s="3">
-        <v>297900</v>
+        <v>300900</v>
       </c>
       <c r="J62" s="3">
-        <v>222600</v>
+        <v>224900</v>
       </c>
       <c r="K62" s="3">
         <v>186600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2761600</v>
+        <v>2789400</v>
       </c>
       <c r="E66" s="3">
-        <v>2772900</v>
+        <v>2800900</v>
       </c>
       <c r="F66" s="3">
-        <v>2367000</v>
+        <v>2390900</v>
       </c>
       <c r="G66" s="3">
-        <v>2060500</v>
+        <v>2081300</v>
       </c>
       <c r="H66" s="3">
-        <v>1208100</v>
+        <v>1220300</v>
       </c>
       <c r="I66" s="3">
-        <v>1234000</v>
+        <v>1246400</v>
       </c>
       <c r="J66" s="3">
-        <v>779600</v>
+        <v>787500</v>
       </c>
       <c r="K66" s="3">
         <v>700400</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1191300</v>
+        <v>1203400</v>
       </c>
       <c r="E72" s="3">
-        <v>1240700</v>
+        <v>1253200</v>
       </c>
       <c r="F72" s="3">
-        <v>1274600</v>
+        <v>1287400</v>
       </c>
       <c r="G72" s="3">
-        <v>460300</v>
+        <v>465000</v>
       </c>
       <c r="H72" s="3">
-        <v>267600</v>
+        <v>270300</v>
       </c>
       <c r="I72" s="3">
-        <v>90700</v>
+        <v>91600</v>
       </c>
       <c r="J72" s="3">
-        <v>-117100</v>
+        <v>-118300</v>
       </c>
       <c r="K72" s="3">
         <v>-287400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3845600</v>
+        <v>3884400</v>
       </c>
       <c r="E76" s="3">
-        <v>3990200</v>
+        <v>4030500</v>
       </c>
       <c r="F76" s="3">
-        <v>3876000</v>
+        <v>3915100</v>
       </c>
       <c r="G76" s="3">
-        <v>2856800</v>
+        <v>2885600</v>
       </c>
       <c r="H76" s="3">
-        <v>2292800</v>
+        <v>2315900</v>
       </c>
       <c r="I76" s="3">
-        <v>1818600</v>
+        <v>1837000</v>
       </c>
       <c r="J76" s="3">
-        <v>1557100</v>
+        <v>1572800</v>
       </c>
       <c r="K76" s="3">
         <v>1416400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>99600</v>
+        <v>100600</v>
       </c>
       <c r="E81" s="3">
-        <v>113500</v>
+        <v>114700</v>
       </c>
       <c r="F81" s="3">
-        <v>954600</v>
+        <v>964300</v>
       </c>
       <c r="G81" s="3">
-        <v>313200</v>
+        <v>316400</v>
       </c>
       <c r="H81" s="3">
-        <v>278400</v>
+        <v>281300</v>
       </c>
       <c r="I81" s="3">
-        <v>339000</v>
+        <v>342400</v>
       </c>
       <c r="J81" s="3">
-        <v>260700</v>
+        <v>263300</v>
       </c>
       <c r="K81" s="3">
         <v>203100</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>228200</v>
+        <v>230500</v>
       </c>
       <c r="E89" s="3">
-        <v>202200</v>
+        <v>204300</v>
       </c>
       <c r="F89" s="3">
-        <v>191100</v>
+        <v>193100</v>
       </c>
       <c r="G89" s="3">
-        <v>178100</v>
+        <v>179800</v>
       </c>
       <c r="H89" s="3">
-        <v>133700</v>
+        <v>135000</v>
       </c>
       <c r="I89" s="3">
-        <v>115100</v>
+        <v>116200</v>
       </c>
       <c r="J89" s="3">
-        <v>115600</v>
+        <v>116800</v>
       </c>
       <c r="K89" s="3">
         <v>116300</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-95600</v>
+        <v>-96600</v>
       </c>
       <c r="E91" s="3">
-        <v>-195300</v>
+        <v>-197300</v>
       </c>
       <c r="F91" s="3">
-        <v>-72700</v>
+        <v>-73400</v>
       </c>
       <c r="G91" s="3">
-        <v>-47600</v>
+        <v>-48100</v>
       </c>
       <c r="H91" s="3">
-        <v>-22200</v>
+        <v>-22400</v>
       </c>
       <c r="I91" s="3">
-        <v>-25200</v>
+        <v>-25400</v>
       </c>
       <c r="J91" s="3">
-        <v>-61000</v>
+        <v>-61600</v>
       </c>
       <c r="K91" s="3">
         <v>-14200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-93400</v>
+        <v>-94300</v>
       </c>
       <c r="E94" s="3">
-        <v>-558600</v>
+        <v>-564300</v>
       </c>
       <c r="F94" s="3">
-        <v>-747300</v>
+        <v>-754800</v>
       </c>
       <c r="G94" s="3">
-        <v>-777500</v>
+        <v>-785300</v>
       </c>
       <c r="H94" s="3">
-        <v>-638500</v>
+        <v>-644900</v>
       </c>
       <c r="I94" s="3">
-        <v>69900</v>
+        <v>70600</v>
       </c>
       <c r="J94" s="3">
-        <v>-173300</v>
+        <v>-175100</v>
       </c>
       <c r="K94" s="3">
         <v>8600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-148600</v>
+        <v>-150100</v>
       </c>
       <c r="E96" s="3">
-        <v>-147400</v>
+        <v>-148900</v>
       </c>
       <c r="F96" s="3">
-        <v>-139300</v>
+        <v>-140700</v>
       </c>
       <c r="G96" s="3">
-        <v>-118800</v>
+        <v>-120000</v>
       </c>
       <c r="H96" s="3">
-        <v>-109800</v>
+        <v>-110900</v>
       </c>
       <c r="I96" s="3">
-        <v>-91200</v>
+        <v>-92100</v>
       </c>
       <c r="J96" s="3">
-        <v>-89400</v>
+        <v>-90300</v>
       </c>
       <c r="K96" s="3">
         <v>-82200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-148000</v>
+        <v>-149500</v>
       </c>
       <c r="E100" s="3">
-        <v>156400</v>
+        <v>157900</v>
       </c>
       <c r="F100" s="3">
-        <v>243000</v>
+        <v>245500</v>
       </c>
       <c r="G100" s="3">
-        <v>989800</v>
+        <v>999800</v>
       </c>
       <c r="H100" s="3">
-        <v>250300</v>
+        <v>252900</v>
       </c>
       <c r="I100" s="3">
-        <v>236300</v>
+        <v>238600</v>
       </c>
       <c r="J100" s="3">
-        <v>-76700</v>
+        <v>-77500</v>
       </c>
       <c r="K100" s="3">
         <v>-29100</v>
@@ -4452,7 +4452,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="E101" s="3">
         <v>5200</v>
@@ -4464,10 +4464,10 @@
         <v>-2300</v>
       </c>
       <c r="H101" s="3">
-        <v>-7600</v>
+        <v>-7700</v>
       </c>
       <c r="I101" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="J101" s="3">
         <v>5300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-13800</v>
+        <v>-13900</v>
       </c>
       <c r="E102" s="3">
-        <v>-194900</v>
+        <v>-196900</v>
       </c>
       <c r="F102" s="3">
-        <v>-312500</v>
+        <v>-315600</v>
       </c>
       <c r="G102" s="3">
-        <v>388100</v>
+        <v>392100</v>
       </c>
       <c r="H102" s="3">
-        <v>-262000</v>
+        <v>-264700</v>
       </c>
       <c r="I102" s="3">
-        <v>429400</v>
+        <v>433700</v>
       </c>
       <c r="J102" s="3">
-        <v>-129100</v>
+        <v>-130400</v>
       </c>
       <c r="K102" s="3">
         <v>92400</v>

--- a/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>GRP.U</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>383700</v>
+        <v>394700</v>
       </c>
       <c r="E8" s="3">
-        <v>335400</v>
+        <v>336600</v>
       </c>
       <c r="F8" s="3">
-        <v>289700</v>
+        <v>310900</v>
       </c>
       <c r="G8" s="3">
-        <v>250400</v>
+        <v>267000</v>
       </c>
       <c r="H8" s="3">
-        <v>201500</v>
+        <v>210300</v>
       </c>
       <c r="I8" s="3">
-        <v>182200</v>
+        <v>180600</v>
       </c>
       <c r="J8" s="3">
-        <v>180100</v>
+        <v>193800</v>
       </c>
       <c r="K8" s="3">
         <v>162400</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>63300</v>
+        <v>65100</v>
       </c>
       <c r="E9" s="3">
-        <v>55400</v>
+        <v>55600</v>
       </c>
       <c r="F9" s="3">
-        <v>44800</v>
+        <v>48100</v>
       </c>
       <c r="G9" s="3">
-        <v>34700</v>
+        <v>37000</v>
       </c>
       <c r="H9" s="3">
-        <v>26000</v>
+        <v>27300</v>
       </c>
       <c r="I9" s="3">
-        <v>22800</v>
+        <v>28500</v>
       </c>
       <c r="J9" s="3">
-        <v>23100</v>
+        <v>25600</v>
       </c>
       <c r="K9" s="3">
         <v>5600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>320400</v>
+        <v>329600</v>
       </c>
       <c r="E10" s="3">
-        <v>280000</v>
+        <v>281000</v>
       </c>
       <c r="F10" s="3">
-        <v>244900</v>
+        <v>262900</v>
       </c>
       <c r="G10" s="3">
-        <v>215700</v>
+        <v>230000</v>
       </c>
       <c r="H10" s="3">
-        <v>175400</v>
+        <v>183100</v>
       </c>
       <c r="I10" s="3">
-        <v>159400</v>
+        <v>152100</v>
       </c>
       <c r="J10" s="3">
-        <v>157000</v>
+        <v>168300</v>
       </c>
       <c r="K10" s="3">
         <v>156900</v>
@@ -969,26 +969,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>131900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>162800</v>
       </c>
       <c r="F14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+        <v>-1022600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-213700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-187500</v>
       </c>
       <c r="I14" s="3">
-        <v>5900</v>
+        <v>-255600</v>
       </c>
       <c r="J14" s="3">
-        <v>500</v>
+        <v>-165400</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
         <v>1200</v>
@@ -1024,7 +1024,7 @@
         <v>1000</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
@@ -1033,7 +1033,7 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>147800</v>
+        <v>97500</v>
       </c>
       <c r="E17" s="3">
-        <v>113700</v>
+        <v>78500</v>
       </c>
       <c r="F17" s="3">
-        <v>102700</v>
+        <v>79400</v>
       </c>
       <c r="G17" s="3">
-        <v>81200</v>
+        <v>63000</v>
       </c>
       <c r="H17" s="3">
-        <v>66000</v>
+        <v>52200</v>
       </c>
       <c r="I17" s="3">
-        <v>58200</v>
+        <v>50300</v>
       </c>
       <c r="J17" s="3">
-        <v>62100</v>
+        <v>46600</v>
       </c>
       <c r="K17" s="3">
         <v>40400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>235900</v>
+        <v>297200</v>
       </c>
       <c r="E18" s="3">
-        <v>221700</v>
+        <v>258100</v>
       </c>
       <c r="F18" s="3">
-        <v>186900</v>
+        <v>231500</v>
       </c>
       <c r="G18" s="3">
-        <v>169200</v>
+        <v>204000</v>
       </c>
       <c r="H18" s="3">
-        <v>135500</v>
+        <v>158200</v>
       </c>
       <c r="I18" s="3">
-        <v>124000</v>
+        <v>130400</v>
       </c>
       <c r="J18" s="3">
-        <v>118000</v>
+        <v>147200</v>
       </c>
       <c r="K18" s="3">
         <v>122100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-140900</v>
+        <v>-1500</v>
       </c>
       <c r="E20" s="3">
-        <v>-153900</v>
+        <v>900</v>
       </c>
       <c r="F20" s="3">
-        <v>954700</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>198100</v>
+        <v>-4900</v>
       </c>
       <c r="H20" s="3">
-        <v>177300</v>
+        <v>3900</v>
       </c>
       <c r="I20" s="3">
-        <v>257300</v>
+        <v>-8100</v>
       </c>
       <c r="J20" s="3">
-        <v>155200</v>
+        <v>1100</v>
       </c>
       <c r="K20" s="3">
         <v>116600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>95900</v>
+        <v>299700</v>
       </c>
       <c r="E21" s="3">
-        <v>69000</v>
+        <v>258400</v>
       </c>
       <c r="F21" s="3">
-        <v>1142600</v>
+        <v>234500</v>
       </c>
       <c r="G21" s="3">
-        <v>368200</v>
+        <v>209700</v>
       </c>
       <c r="H21" s="3">
-        <v>313500</v>
+        <v>154900</v>
       </c>
       <c r="I21" s="3">
-        <v>381500</v>
+        <v>138700</v>
       </c>
       <c r="J21" s="3">
-        <v>273500</v>
+        <v>146400</v>
       </c>
       <c r="K21" s="3">
         <v>239200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>70600</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>23200</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>95000</v>
+        <v>97700</v>
       </c>
       <c r="E23" s="3">
-        <v>67800</v>
+        <v>68100</v>
       </c>
       <c r="F23" s="3">
-        <v>1141600</v>
+        <v>1225500</v>
       </c>
       <c r="G23" s="3">
-        <v>367300</v>
+        <v>391600</v>
       </c>
       <c r="H23" s="3">
-        <v>312800</v>
+        <v>327600</v>
       </c>
       <c r="I23" s="3">
-        <v>381300</v>
+        <v>379600</v>
       </c>
       <c r="J23" s="3">
-        <v>273200</v>
+        <v>296000</v>
       </c>
       <c r="K23" s="3">
         <v>238700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-7000</v>
+        <v>-7200</v>
       </c>
       <c r="E24" s="3">
-        <v>-46900</v>
+        <v>-47000</v>
       </c>
       <c r="F24" s="3">
-        <v>177100</v>
+        <v>190100</v>
       </c>
       <c r="G24" s="3">
-        <v>50900</v>
+        <v>54200</v>
       </c>
       <c r="H24" s="3">
-        <v>31400</v>
+        <v>32900</v>
       </c>
       <c r="I24" s="3">
-        <v>38800</v>
+        <v>38600</v>
       </c>
       <c r="J24" s="3">
-        <v>9900</v>
+        <v>10700</v>
       </c>
       <c r="K24" s="3">
         <v>34600</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>101900</v>
+        <v>104900</v>
       </c>
       <c r="E26" s="3">
-        <v>114700</v>
+        <v>115100</v>
       </c>
       <c r="F26" s="3">
-        <v>964500</v>
+        <v>1035400</v>
       </c>
       <c r="G26" s="3">
-        <v>316500</v>
+        <v>337400</v>
       </c>
       <c r="H26" s="3">
-        <v>281400</v>
+        <v>294700</v>
       </c>
       <c r="I26" s="3">
-        <v>342600</v>
+        <v>341000</v>
       </c>
       <c r="J26" s="3">
-        <v>263300</v>
+        <v>285300</v>
       </c>
       <c r="K26" s="3">
         <v>204100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100600</v>
+        <v>103500</v>
       </c>
       <c r="E27" s="3">
-        <v>114700</v>
+        <v>115100</v>
       </c>
       <c r="F27" s="3">
-        <v>964300</v>
+        <v>1035100</v>
       </c>
       <c r="G27" s="3">
-        <v>316400</v>
+        <v>337300</v>
       </c>
       <c r="H27" s="3">
-        <v>281300</v>
+        <v>294600</v>
       </c>
       <c r="I27" s="3">
-        <v>342400</v>
+        <v>340900</v>
       </c>
       <c r="J27" s="3">
-        <v>263300</v>
+        <v>285300</v>
       </c>
       <c r="K27" s="3">
         <v>203100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>140900</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>153900</v>
+        <v>-900</v>
       </c>
       <c r="F32" s="3">
-        <v>-954700</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>-198100</v>
+        <v>4900</v>
       </c>
       <c r="H32" s="3">
-        <v>-177300</v>
+        <v>-3900</v>
       </c>
       <c r="I32" s="3">
-        <v>-257300</v>
+        <v>8100</v>
       </c>
       <c r="J32" s="3">
-        <v>-155200</v>
+        <v>-1100</v>
       </c>
       <c r="K32" s="3">
         <v>-116600</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100600</v>
+        <v>103500</v>
       </c>
       <c r="E33" s="3">
-        <v>114700</v>
+        <v>115100</v>
       </c>
       <c r="F33" s="3">
-        <v>964300</v>
+        <v>1035100</v>
       </c>
       <c r="G33" s="3">
-        <v>316400</v>
+        <v>337300</v>
       </c>
       <c r="H33" s="3">
-        <v>281300</v>
+        <v>294600</v>
       </c>
       <c r="I33" s="3">
-        <v>342400</v>
+        <v>340900</v>
       </c>
       <c r="J33" s="3">
-        <v>263300</v>
+        <v>285300</v>
       </c>
       <c r="K33" s="3">
         <v>203100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100600</v>
+        <v>103500</v>
       </c>
       <c r="E35" s="3">
-        <v>114700</v>
+        <v>115100</v>
       </c>
       <c r="F35" s="3">
-        <v>964300</v>
+        <v>1035100</v>
       </c>
       <c r="G35" s="3">
-        <v>316400</v>
+        <v>337300</v>
       </c>
       <c r="H35" s="3">
-        <v>281300</v>
+        <v>294600</v>
       </c>
       <c r="I35" s="3">
-        <v>342400</v>
+        <v>340900</v>
       </c>
       <c r="J35" s="3">
-        <v>263300</v>
+        <v>285300</v>
       </c>
       <c r="K35" s="3">
         <v>203100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>85200</v>
+        <v>87900</v>
       </c>
       <c r="E41" s="3">
-        <v>93600</v>
+        <v>99800</v>
       </c>
       <c r="F41" s="3">
-        <v>295900</v>
+        <v>318100</v>
       </c>
       <c r="G41" s="3">
-        <v>574900</v>
+        <v>652400</v>
       </c>
       <c r="H41" s="3">
-        <v>182900</v>
+        <v>230300</v>
       </c>
       <c r="I41" s="3">
-        <v>393800</v>
+        <v>482400</v>
       </c>
       <c r="J41" s="3">
-        <v>40900</v>
+        <v>55000</v>
       </c>
       <c r="K41" s="3">
         <v>79500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>6800</v>
       </c>
       <c r="E42" s="3">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>36900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>90700</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>99500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9400</v>
+        <v>9700</v>
       </c>
       <c r="E43" s="3">
-        <v>60800</v>
+        <v>61100</v>
       </c>
       <c r="F43" s="3">
-        <v>9000</v>
+        <v>9600</v>
       </c>
       <c r="G43" s="3">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="3">
-        <v>14600</v>
+        <v>15200</v>
       </c>
       <c r="I43" s="3">
         <v>3300</v>
       </c>
       <c r="J43" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="K43" s="3">
         <v>1100</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16800</v>
+        <v>10400</v>
       </c>
       <c r="E45" s="3">
-        <v>41100</v>
+        <v>41300</v>
       </c>
       <c r="F45" s="3">
-        <v>52900</v>
+        <v>56700</v>
       </c>
       <c r="G45" s="3">
-        <v>5100</v>
+        <v>5400</v>
       </c>
       <c r="H45" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I45" s="3">
-        <v>34800</v>
+        <v>34300</v>
       </c>
       <c r="J45" s="3">
-        <v>290000</v>
+        <v>313800</v>
       </c>
       <c r="K45" s="3">
         <v>2200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>111700</v>
+        <v>114900</v>
       </c>
       <c r="E46" s="3">
-        <v>201400</v>
+        <v>202200</v>
       </c>
       <c r="F46" s="3">
-        <v>358100</v>
+        <v>384500</v>
       </c>
       <c r="G46" s="3">
-        <v>622600</v>
+        <v>663800</v>
       </c>
       <c r="H46" s="3">
-        <v>236900</v>
+        <v>248100</v>
       </c>
       <c r="I46" s="3">
-        <v>522600</v>
+        <v>520300</v>
       </c>
       <c r="J46" s="3">
-        <v>342700</v>
+        <v>371200</v>
       </c>
       <c r="K46" s="3">
         <v>182200</v>
@@ -2263,16 +2263,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>200</v>
+        <v>75900</v>
       </c>
       <c r="E47" s="3">
-        <v>200</v>
+        <v>112200</v>
       </c>
       <c r="F47" s="3">
-        <v>7900</v>
+        <v>49600</v>
       </c>
       <c r="G47" s="3">
-        <v>300</v>
+        <v>22500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6486100</v>
+        <v>6637300</v>
       </c>
       <c r="E48" s="3">
-        <v>6509900</v>
+        <v>6474400</v>
       </c>
       <c r="F48" s="3">
-        <v>5869500</v>
+        <v>6236800</v>
       </c>
       <c r="G48" s="3">
-        <v>4312800</v>
+        <v>4568400</v>
       </c>
       <c r="H48" s="3">
-        <v>3283100</v>
+        <v>3416300</v>
       </c>
       <c r="I48" s="3">
-        <v>2521700</v>
+        <v>2507600</v>
       </c>
       <c r="J48" s="3">
-        <v>2012900</v>
+        <v>2165400</v>
       </c>
       <c r="K48" s="3">
         <v>1929400</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>75900</v>
+        <v>34900</v>
       </c>
       <c r="E52" s="3">
-        <v>119900</v>
+        <v>66300</v>
       </c>
       <c r="F52" s="3">
-        <v>70500</v>
+        <v>93100</v>
       </c>
       <c r="G52" s="3">
-        <v>31200</v>
+        <v>36500</v>
       </c>
       <c r="H52" s="3">
-        <v>16300</v>
+        <v>35600</v>
       </c>
       <c r="I52" s="3">
-        <v>39000</v>
+        <v>37000</v>
       </c>
       <c r="J52" s="3">
-        <v>4700</v>
+        <v>15400</v>
       </c>
       <c r="K52" s="3">
         <v>4800</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6673900</v>
+        <v>6865200</v>
       </c>
       <c r="E54" s="3">
-        <v>6831400</v>
+        <v>6857000</v>
       </c>
       <c r="F54" s="3">
-        <v>6306000</v>
+        <v>6769500</v>
       </c>
       <c r="G54" s="3">
-        <v>4966900</v>
+        <v>5295500</v>
       </c>
       <c r="H54" s="3">
-        <v>3536200</v>
+        <v>3703800</v>
       </c>
       <c r="I54" s="3">
-        <v>3083400</v>
+        <v>3069700</v>
       </c>
       <c r="J54" s="3">
-        <v>2360300</v>
+        <v>2556800</v>
       </c>
       <c r="K54" s="3">
         <v>2116800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="E57" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="F57" s="3">
-        <v>4000</v>
+        <v>6300</v>
       </c>
       <c r="G57" s="3">
-        <v>7300</v>
+        <v>3000</v>
       </c>
       <c r="H57" s="3">
-        <v>5000</v>
+        <v>5300</v>
       </c>
       <c r="I57" s="3">
         <v>3900</v>
       </c>
       <c r="J57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="K57" s="3">
         <v>4100</v>
@@ -2706,16 +2706,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>180300</v>
+        <v>185400</v>
       </c>
       <c r="E58" s="3">
-        <v>332600</v>
+        <v>339100</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>184500</v>
+        <v>210100</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>94400</v>
+        <v>54400</v>
       </c>
       <c r="E59" s="3">
-        <v>115000</v>
+        <v>73700</v>
       </c>
       <c r="F59" s="3">
-        <v>116700</v>
+        <v>82800</v>
       </c>
       <c r="G59" s="3">
-        <v>83400</v>
+        <v>47100</v>
       </c>
       <c r="H59" s="3">
-        <v>57100</v>
+        <v>35600</v>
       </c>
       <c r="I59" s="3">
-        <v>58400</v>
+        <v>38600</v>
       </c>
       <c r="J59" s="3">
-        <v>57100</v>
+        <v>41800</v>
       </c>
       <c r="K59" s="3">
         <v>38400</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>283000</v>
+        <v>291100</v>
       </c>
       <c r="E60" s="3">
-        <v>455900</v>
+        <v>457600</v>
       </c>
       <c r="F60" s="3">
-        <v>121000</v>
+        <v>129900</v>
       </c>
       <c r="G60" s="3">
-        <v>275200</v>
+        <v>293500</v>
       </c>
       <c r="H60" s="3">
-        <v>62600</v>
+        <v>65600</v>
       </c>
       <c r="I60" s="3">
-        <v>62300</v>
+        <v>62000</v>
       </c>
       <c r="J60" s="3">
-        <v>85200</v>
+        <v>92300</v>
       </c>
       <c r="K60" s="3">
         <v>42500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2101100</v>
+        <v>2167700</v>
       </c>
       <c r="E61" s="3">
-        <v>1926300</v>
+        <v>1938300</v>
       </c>
       <c r="F61" s="3">
-        <v>1809000</v>
+        <v>1956600</v>
       </c>
       <c r="G61" s="3">
-        <v>1443700</v>
+        <v>1615500</v>
       </c>
       <c r="H61" s="3">
-        <v>897600</v>
+        <v>963600</v>
       </c>
       <c r="I61" s="3">
-        <v>882200</v>
+        <v>955000</v>
       </c>
       <c r="J61" s="3">
-        <v>476500</v>
+        <v>565200</v>
       </c>
       <c r="K61" s="3">
         <v>470200</v>
@@ -2885,26 +2885,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>415000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>458800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>360800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>258600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>300900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>224900</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>186600</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2789400</v>
+        <v>2864300</v>
       </c>
       <c r="E66" s="3">
-        <v>2800900</v>
+        <v>2807700</v>
       </c>
       <c r="F66" s="3">
-        <v>2390900</v>
+        <v>2564400</v>
       </c>
       <c r="G66" s="3">
-        <v>2081300</v>
+        <v>2217300</v>
       </c>
       <c r="H66" s="3">
-        <v>1220300</v>
+        <v>1276600</v>
       </c>
       <c r="I66" s="3">
-        <v>1246400</v>
+        <v>1239800</v>
       </c>
       <c r="J66" s="3">
-        <v>787500</v>
+        <v>852100</v>
       </c>
       <c r="K66" s="3">
         <v>700400</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1203400</v>
+        <v>1237900</v>
       </c>
       <c r="E72" s="3">
-        <v>1253200</v>
+        <v>1257900</v>
       </c>
       <c r="F72" s="3">
-        <v>1287400</v>
+        <v>1382000</v>
       </c>
       <c r="G72" s="3">
-        <v>465000</v>
+        <v>495700</v>
       </c>
       <c r="H72" s="3">
-        <v>270300</v>
+        <v>283100</v>
       </c>
       <c r="I72" s="3">
-        <v>91600</v>
+        <v>91200</v>
       </c>
       <c r="J72" s="3">
-        <v>-118300</v>
+        <v>-128100</v>
       </c>
       <c r="K72" s="3">
         <v>-287400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3884400</v>
+        <v>3995800</v>
       </c>
       <c r="E76" s="3">
-        <v>4030500</v>
+        <v>4045600</v>
       </c>
       <c r="F76" s="3">
-        <v>3915100</v>
+        <v>4202800</v>
       </c>
       <c r="G76" s="3">
-        <v>2885600</v>
+        <v>3076500</v>
       </c>
       <c r="H76" s="3">
-        <v>2315900</v>
+        <v>2425600</v>
       </c>
       <c r="I76" s="3">
-        <v>1837000</v>
+        <v>1828800</v>
       </c>
       <c r="J76" s="3">
-        <v>1572800</v>
+        <v>1703700</v>
       </c>
       <c r="K76" s="3">
         <v>1416400</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100600</v>
+        <v>103500</v>
       </c>
       <c r="E81" s="3">
-        <v>114700</v>
+        <v>115100</v>
       </c>
       <c r="F81" s="3">
-        <v>964300</v>
+        <v>1035100</v>
       </c>
       <c r="G81" s="3">
-        <v>316400</v>
+        <v>337300</v>
       </c>
       <c r="H81" s="3">
-        <v>281300</v>
+        <v>294600</v>
       </c>
       <c r="I81" s="3">
-        <v>342400</v>
+        <v>340900</v>
       </c>
       <c r="J81" s="3">
-        <v>263300</v>
+        <v>285300</v>
       </c>
       <c r="K81" s="3">
         <v>203100</v>
@@ -3694,7 +3694,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>1200</v>
@@ -3703,7 +3703,7 @@
         <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
@@ -3712,7 +3712,7 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>230500</v>
+        <v>237100</v>
       </c>
       <c r="E89" s="3">
-        <v>204300</v>
+        <v>205000</v>
       </c>
       <c r="F89" s="3">
-        <v>193100</v>
+        <v>207200</v>
       </c>
       <c r="G89" s="3">
-        <v>179800</v>
+        <v>195600</v>
       </c>
       <c r="H89" s="3">
-        <v>135000</v>
+        <v>141400</v>
       </c>
       <c r="I89" s="3">
-        <v>116200</v>
+        <v>115700</v>
       </c>
       <c r="J89" s="3">
-        <v>116800</v>
+        <v>126500</v>
       </c>
       <c r="K89" s="3">
         <v>116300</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-96600</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-197300</v>
+        <v>-600</v>
       </c>
       <c r="F91" s="3">
-        <v>-73400</v>
+        <v>-500</v>
       </c>
       <c r="G91" s="3">
-        <v>-48100</v>
+        <v>-1300</v>
       </c>
       <c r="H91" s="3">
-        <v>-22400</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>-25400</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-61600</v>
+        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-14200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-94300</v>
+        <v>-97000</v>
       </c>
       <c r="E94" s="3">
-        <v>-564300</v>
+        <v>-566400</v>
       </c>
       <c r="F94" s="3">
-        <v>-754800</v>
+        <v>-810300</v>
       </c>
       <c r="G94" s="3">
-        <v>-785300</v>
+        <v>-841200</v>
       </c>
       <c r="H94" s="3">
-        <v>-644900</v>
+        <v>-675500</v>
       </c>
       <c r="I94" s="3">
-        <v>70600</v>
+        <v>70300</v>
       </c>
       <c r="J94" s="3">
-        <v>-175100</v>
+        <v>-189700</v>
       </c>
       <c r="K94" s="3">
         <v>8600</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-150100</v>
+        <v>154400</v>
       </c>
       <c r="E96" s="3">
-        <v>-148900</v>
+        <v>149500</v>
       </c>
       <c r="F96" s="3">
-        <v>-140700</v>
+        <v>151000</v>
       </c>
       <c r="G96" s="3">
-        <v>-120000</v>
+        <v>128000</v>
       </c>
       <c r="H96" s="3">
-        <v>-110900</v>
+        <v>105500</v>
       </c>
       <c r="I96" s="3">
-        <v>-92100</v>
+        <v>91700</v>
       </c>
       <c r="J96" s="3">
-        <v>-90300</v>
+        <v>97800</v>
       </c>
       <c r="K96" s="3">
         <v>-82200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-149500</v>
+        <v>-153800</v>
       </c>
       <c r="E100" s="3">
-        <v>157900</v>
+        <v>158500</v>
       </c>
       <c r="F100" s="3">
-        <v>245500</v>
+        <v>263500</v>
       </c>
       <c r="G100" s="3">
-        <v>999800</v>
+        <v>1065900</v>
       </c>
       <c r="H100" s="3">
-        <v>252900</v>
+        <v>264900</v>
       </c>
       <c r="I100" s="3">
-        <v>238600</v>
+        <v>237600</v>
       </c>
       <c r="J100" s="3">
-        <v>-77500</v>
+        <v>-83900</v>
       </c>
       <c r="K100" s="3">
         <v>-29100</v>
@@ -4461,16 +4461,16 @@
         <v>700</v>
       </c>
       <c r="G101" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="H101" s="3">
-        <v>-7700</v>
+        <v>-8000</v>
       </c>
       <c r="I101" s="3">
         <v>8300</v>
       </c>
       <c r="J101" s="3">
-        <v>5300</v>
+        <v>5800</v>
       </c>
       <c r="K101" s="3">
         <v>-3500</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-13900</v>
+        <v>-14300</v>
       </c>
       <c r="E102" s="3">
-        <v>-196900</v>
+        <v>-197600</v>
       </c>
       <c r="F102" s="3">
-        <v>-315600</v>
+        <v>-338800</v>
       </c>
       <c r="G102" s="3">
-        <v>392100</v>
+        <v>418000</v>
       </c>
       <c r="H102" s="3">
-        <v>-264700</v>
+        <v>-277200</v>
       </c>
       <c r="I102" s="3">
-        <v>433700</v>
+        <v>431800</v>
       </c>
       <c r="J102" s="3">
-        <v>-130400</v>
+        <v>-141300</v>
       </c>
       <c r="K102" s="3">
         <v>92400</v>

--- a/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GRP.U_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>GRP.U</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>395200</v>
+      </c>
+      <c r="E8" s="3">
         <v>394700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>336600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>310900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>267000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>210300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>180600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>193800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>162400</v>
       </c>
       <c r="L8" s="3">
         <v>162400</v>
       </c>
       <c r="M8" s="3">
+        <v>162400</v>
+      </c>
+      <c r="N8" s="3">
         <v>162800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>146200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>136300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E9" s="3">
         <v>65100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>37000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>36400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32800</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>327700</v>
+      </c>
+      <c r="E10" s="3">
         <v>329600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>281000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>262900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>230000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>183100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>152100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>168300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>156900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>157100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>157400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>137600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>99900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>106200</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,80 +979,86 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>131900</v>
+        <v>-34800</v>
       </c>
       <c r="E14" s="3">
+        <v>132000</v>
+      </c>
+      <c r="F14" s="3">
         <v>162800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1022600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-213700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-187500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-255600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-165400</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>15000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>500</v>
       </c>
       <c r="L15" s="3">
         <v>500</v>
@@ -1045,17 +1067,20 @@
         <v>500</v>
       </c>
       <c r="N15" s="3">
+        <v>500</v>
+      </c>
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>97500</v>
+        <v>93000</v>
       </c>
       <c r="E17" s="3">
+        <v>97400</v>
+      </c>
+      <c r="F17" s="3">
         <v>78500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>63000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>97900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>297200</v>
+        <v>302200</v>
       </c>
       <c r="E18" s="3">
+        <v>297300</v>
+      </c>
+      <c r="F18" s="3">
         <v>258100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>231500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>204000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>158200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>130400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>147200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>122100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>121500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>118400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>94000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>96800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,125 +1211,132 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>116600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>52500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-61700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>299700</v>
+        <v>291700</v>
       </c>
       <c r="E21" s="3">
+        <v>299800</v>
+      </c>
+      <c r="F21" s="3">
         <v>258400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>234500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>209700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>154900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>138700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>146400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>239200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>174500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>57100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>85300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>121800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>74100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E22" s="3">
         <v>70600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13900</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E23" s="3">
         <v>97700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1225500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>391600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>327600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>379600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>296000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>238700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>174000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>56600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>84900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-47000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>190100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>54200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-25500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E26" s="3">
         <v>104900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>115100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1035400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>337400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>294700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>341000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>285300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>204100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>146800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>50000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>112800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>44500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E27" s="3">
         <v>103500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>115100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1035100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>337300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>294600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>340900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>285300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>203100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>145200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,24 +1673,27 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>1400</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>72600</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-116600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-52500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>61700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E33" s="3">
         <v>103500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>115100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1035100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>337300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>294600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>340900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>285300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>203100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>145200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>55100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>111600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117100</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E35" s="3">
         <v>103500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>115100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1035100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>337300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>294600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>340900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>285300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>203100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>145200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>55100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>111600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117100</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,62 +2072,66 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E41" s="3">
         <v>87900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>318100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>652400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>230300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>482400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>48400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>73500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>6800</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2059,13 +2148,13 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>99500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>41100</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
@@ -2076,54 +2165,60 @@
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E43" s="3">
         <v>9700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,8 +2243,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2166,116 +2261,125 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>313800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E46" s="3">
         <v>114900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>202200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>384500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>663800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>248100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>520300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>371200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>182200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>99000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>80600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E47" s="3">
         <v>75900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>112200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>22500</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -2283,8 +2387,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>400</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>400</v>
@@ -2296,59 +2400,65 @@
         <v>400</v>
       </c>
       <c r="O47" s="3">
+        <v>400</v>
+      </c>
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2300</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6637300</v>
+        <v>6533900</v>
       </c>
       <c r="E48" s="3">
+        <v>6672000</v>
+      </c>
+      <c r="F48" s="3">
         <v>6474400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6236800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4568400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3416300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2507600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2165400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1929400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1947400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1815100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1812000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2321200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>515800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2391,9 +2501,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>34900</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>66300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>93100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>36500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>37000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6685800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6865200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6857000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6769500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5295500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3703800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3069700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2556800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2116800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2051200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1921600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1900400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1510900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>956800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,233 +2784,249 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>185400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>339100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>210100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>26000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>30200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E59" s="3">
         <v>54400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>38600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>41800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>36800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>57600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E60" s="3">
         <v>291100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>457600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>129900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>293500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>62000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>92300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>42500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>77500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2185200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2167700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1938300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1956600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1615500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>963600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>955000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>565200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>470200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>393300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>402200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>387900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>198400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>202200</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2906,27 +3051,30 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>186600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>184800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>133700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>139600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>143000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2698800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2864300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2807700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2564400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2217300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1276600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1239800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>852100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>700400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>662900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>642000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>613900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>370600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>258300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1242100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1237900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1257900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1382000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>495700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>283100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>91200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-128100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-287400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-418300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-504100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-468600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-492900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-673300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3981100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3995800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4045600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4202800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3076500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2425600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1828800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1703700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1416400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1388400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1279600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1286500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1140300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>698500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E81" s="3">
         <v>103500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>115100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1035100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>337300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>294600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>340900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>285300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>203100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>145200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>55100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>111600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117100</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,34 +3885,35 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
@@ -3724,17 +3922,20 @@
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E89" s="3">
         <v>237100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>205000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>207200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>195600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>141400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>115700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>126500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>116300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>120000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>72900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>87400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>86000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-97000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-566400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-810300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-841200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-675500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>70300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-189700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>8600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>15800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-195200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-73900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>144500</v>
+      </c>
+      <c r="E96" s="3">
         <v>154400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>149500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>151000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>128000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>105500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>91700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>97800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-82200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-81300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-81000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-69500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-70600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-185900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-153800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>158500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>263500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1065900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>264900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>237600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-83900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-29100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-71200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>124800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-72200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-197600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-338800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>418000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-277200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>431800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-141300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>92400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
